--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -1860,7 +1860,7 @@
         <v>119404184</v>
       </c>
       <c r="B13" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -1860,7 +1860,7 @@
         <v>119404184</v>
       </c>
       <c r="B13" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3696,6 +3696,1144 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123256126</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>596202</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7033790</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123255986</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79876</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>596183</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7033741</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123256408</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>596171</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7033849</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123255234</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>596160</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7033817</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123255552</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>596192</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7033765</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123255893</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>596178</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7033743</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123254018</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>596115</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7033816</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123255954</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91243</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>596185</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7033739</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123253931</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>596135</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7033851</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123256248</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>596180</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7033809</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123255199</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>596170</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7033820</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123256126</v>
+        <v>123254018</v>
       </c>
       <c r="B31" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596202</v>
+        <v>596115</v>
       </c>
       <c r="R31" t="n">
-        <v>7033790</v>
+        <v>7033816</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123256408</v>
+        <v>123256248</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,38 +3914,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596171</v>
+        <v>596180</v>
       </c>
       <c r="R33" t="n">
-        <v>7033849</v>
+        <v>7033809</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4004,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123255234</v>
+        <v>123255552</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4016,42 +4020,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596160</v>
+        <v>596192</v>
       </c>
       <c r="R34" t="n">
-        <v>7033817</v>
+        <v>7033765</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123255552</v>
+        <v>123256126</v>
       </c>
       <c r="B35" t="n">
         <v>90952</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596192</v>
+        <v>596202</v>
       </c>
       <c r="R35" t="n">
-        <v>7033765</v>
+        <v>7033790</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4212,10 +4212,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123255893</v>
+        <v>123255954</v>
       </c>
       <c r="B36" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4224,42 +4224,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596178</v>
+        <v>596185</v>
       </c>
       <c r="R36" t="n">
-        <v>7033743</v>
+        <v>7033739</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4318,10 +4314,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123254018</v>
+        <v>123255893</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4330,38 +4326,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596115</v>
+        <v>596178</v>
       </c>
       <c r="R37" t="n">
-        <v>7033816</v>
+        <v>7033743</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123255954</v>
+        <v>123256408</v>
       </c>
       <c r="B38" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596185</v>
+        <v>596171</v>
       </c>
       <c r="R38" t="n">
-        <v>7033739</v>
+        <v>7033849</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4624,7 +4624,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123256248</v>
+        <v>123255234</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596180</v>
+        <v>596160</v>
       </c>
       <c r="R40" t="n">
-        <v>7033809</v>
+        <v>7033817</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,7 +3698,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123254018</v>
+        <v>123253931</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596115</v>
+        <v>596135</v>
       </c>
       <c r="R31" t="n">
-        <v>7033816</v>
+        <v>7033851</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123255986</v>
+        <v>123254018</v>
       </c>
       <c r="B32" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596183</v>
+        <v>596115</v>
       </c>
       <c r="R32" t="n">
-        <v>7033741</v>
+        <v>7033816</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123256248</v>
+        <v>123255199</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596180</v>
+        <v>596170</v>
       </c>
       <c r="R33" t="n">
-        <v>7033809</v>
+        <v>7033820</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4008,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123255552</v>
+        <v>123255954</v>
       </c>
       <c r="B34" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596192</v>
+        <v>596185</v>
       </c>
       <c r="R34" t="n">
-        <v>7033765</v>
+        <v>7033739</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123256126</v>
+        <v>123256408</v>
       </c>
       <c r="B35" t="n">
         <v>90952</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596202</v>
+        <v>596171</v>
       </c>
       <c r="R35" t="n">
-        <v>7033790</v>
+        <v>7033849</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4212,10 +4212,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123255954</v>
+        <v>123256126</v>
       </c>
       <c r="B36" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,21 +4228,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4252,10 +4252,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596185</v>
+        <v>596202</v>
       </c>
       <c r="R36" t="n">
-        <v>7033739</v>
+        <v>7033790</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123255893</v>
+        <v>123256248</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596178</v>
+        <v>596180</v>
       </c>
       <c r="R37" t="n">
-        <v>7033743</v>
+        <v>7033809</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123256408</v>
+        <v>123255986</v>
       </c>
       <c r="B38" t="n">
-        <v>90952</v>
+        <v>79876</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4432,25 +4432,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596171</v>
+        <v>596183</v>
       </c>
       <c r="R38" t="n">
-        <v>7033849</v>
+        <v>7033741</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123253931</v>
+        <v>123255552</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596135</v>
+        <v>596192</v>
       </c>
       <c r="R39" t="n">
-        <v>7033851</v>
+        <v>7033765</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4624,7 +4624,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123255234</v>
+        <v>123255893</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596160</v>
+        <v>596178</v>
       </c>
       <c r="R40" t="n">
-        <v>7033817</v>
+        <v>7033743</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123255199</v>
+        <v>123255234</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596170</v>
+        <v>596160</v>
       </c>
       <c r="R41" t="n">
-        <v>7033820</v>
+        <v>7033817</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255199</v>
+        <v>123255954</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,42 +3914,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596170</v>
+        <v>596185</v>
       </c>
       <c r="R33" t="n">
-        <v>7033820</v>
+        <v>7033739</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4008,10 +4004,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123255954</v>
+        <v>123255199</v>
       </c>
       <c r="B34" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,38 +4016,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596185</v>
+        <v>596170</v>
       </c>
       <c r="R34" t="n">
-        <v>7033739</v>
+        <v>7033820</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255954</v>
+        <v>123255199</v>
       </c>
       <c r="B33" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,38 +3914,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596185</v>
+        <v>596170</v>
       </c>
       <c r="R33" t="n">
-        <v>7033739</v>
+        <v>7033820</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4004,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123255199</v>
+        <v>123255954</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4016,42 +4020,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596170</v>
+        <v>596185</v>
       </c>
       <c r="R34" t="n">
-        <v>7033820</v>
+        <v>7033739</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3701,7 +3701,7 @@
         <v>123253931</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123254018</v>
+        <v>123256126</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>90955</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596115</v>
+        <v>596202</v>
       </c>
       <c r="R32" t="n">
-        <v>7033816</v>
+        <v>7033790</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255954</v>
+        <v>123255986</v>
       </c>
       <c r="B33" t="n">
-        <v>91243</v>
+        <v>79879</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596185</v>
+        <v>596183</v>
       </c>
       <c r="R33" t="n">
-        <v>7033739</v>
+        <v>7033741</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4007,7 +4007,7 @@
         <v>123255199</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123256408</v>
+        <v>123255234</v>
       </c>
       <c r="B35" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4122,38 +4122,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596171</v>
+        <v>596160</v>
       </c>
       <c r="R35" t="n">
-        <v>7033849</v>
+        <v>7033817</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4212,10 +4216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123256126</v>
+        <v>123254018</v>
       </c>
       <c r="B36" t="n">
-        <v>90952</v>
+        <v>79850</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,21 +4232,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4252,10 +4256,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596202</v>
+        <v>596115</v>
       </c>
       <c r="R36" t="n">
-        <v>7033790</v>
+        <v>7033816</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4317,7 +4321,7 @@
         <v>123256248</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4420,10 +4424,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123255986</v>
+        <v>123255954</v>
       </c>
       <c r="B38" t="n">
-        <v>79876</v>
+        <v>91242</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4432,25 +4436,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4460,10 +4464,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596183</v>
+        <v>596185</v>
       </c>
       <c r="R38" t="n">
-        <v>7033741</v>
+        <v>7033739</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4522,10 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123255552</v>
+        <v>123255893</v>
       </c>
       <c r="B39" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4534,38 +4538,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596192</v>
+        <v>596178</v>
       </c>
       <c r="R39" t="n">
-        <v>7033765</v>
+        <v>7033743</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4624,10 +4632,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123255893</v>
+        <v>123255552</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4636,42 +4644,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596178</v>
+        <v>596192</v>
       </c>
       <c r="R40" t="n">
-        <v>7033743</v>
+        <v>7033765</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4730,10 +4734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123255234</v>
+        <v>123256408</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4742,42 +4746,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596160</v>
+        <v>596171</v>
       </c>
       <c r="R41" t="n">
-        <v>7033817</v>
+        <v>7033849</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123253931</v>
+        <v>123255986</v>
       </c>
       <c r="B31" t="n">
-        <v>79850</v>
+        <v>79881</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,25 +3710,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596135</v>
+        <v>596183</v>
       </c>
       <c r="R31" t="n">
-        <v>7033851</v>
+        <v>7033741</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123256126</v>
+        <v>123256248</v>
       </c>
       <c r="B32" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,38 +3812,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596202</v>
+        <v>596180</v>
       </c>
       <c r="R32" t="n">
-        <v>7033790</v>
+        <v>7033809</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3902,10 +3906,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255986</v>
+        <v>123255552</v>
       </c>
       <c r="B33" t="n">
-        <v>79879</v>
+        <v>90957</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,25 +3918,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3946,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596183</v>
+        <v>596192</v>
       </c>
       <c r="R33" t="n">
-        <v>7033741</v>
+        <v>7033765</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4004,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123255199</v>
+        <v>123256126</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4016,42 +4020,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596170</v>
+        <v>596202</v>
       </c>
       <c r="R34" t="n">
-        <v>7033820</v>
+        <v>7033790</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123255234</v>
+        <v>123253931</v>
       </c>
       <c r="B35" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4122,42 +4122,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596160</v>
+        <v>596135</v>
       </c>
       <c r="R35" t="n">
-        <v>7033817</v>
+        <v>7033851</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4216,10 +4212,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123254018</v>
+        <v>123255893</v>
       </c>
       <c r="B36" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,38 +4224,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596115</v>
+        <v>596178</v>
       </c>
       <c r="R36" t="n">
-        <v>7033816</v>
+        <v>7033743</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4318,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123256248</v>
+        <v>123255199</v>
       </c>
       <c r="B37" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596180</v>
+        <v>596170</v>
       </c>
       <c r="R37" t="n">
-        <v>7033809</v>
+        <v>7033820</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123255954</v>
+        <v>123255234</v>
       </c>
       <c r="B38" t="n">
-        <v>91242</v>
+        <v>98370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4436,38 +4436,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596185</v>
+        <v>596160</v>
       </c>
       <c r="R38" t="n">
-        <v>7033739</v>
+        <v>7033817</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4526,10 +4530,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123255893</v>
+        <v>123255954</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>91244</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4538,42 +4542,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596178</v>
+        <v>596185</v>
       </c>
       <c r="R39" t="n">
-        <v>7033743</v>
+        <v>7033739</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123255552</v>
+        <v>123256408</v>
       </c>
       <c r="B40" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596192</v>
+        <v>596171</v>
       </c>
       <c r="R40" t="n">
-        <v>7033765</v>
+        <v>7033849</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4734,10 +4734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123256408</v>
+        <v>123254018</v>
       </c>
       <c r="B41" t="n">
-        <v>90955</v>
+        <v>79852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4750,21 +4750,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596171</v>
+        <v>596115</v>
       </c>
       <c r="R41" t="n">
-        <v>7033849</v>
+        <v>7033816</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123255986</v>
+        <v>123256248</v>
       </c>
       <c r="B31" t="n">
-        <v>79881</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,38 +3710,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596183</v>
+        <v>596180</v>
       </c>
       <c r="R31" t="n">
-        <v>7033741</v>
+        <v>7033809</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3800,10 +3804,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123256248</v>
+        <v>123255986</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>79881</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,42 +3816,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596180</v>
+        <v>596183</v>
       </c>
       <c r="R32" t="n">
-        <v>7033809</v>
+        <v>7033741</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123256248</v>
+        <v>123255234</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596180</v>
+        <v>596160</v>
       </c>
       <c r="R31" t="n">
-        <v>7033809</v>
+        <v>7033817</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123255986</v>
+        <v>123255893</v>
       </c>
       <c r="B32" t="n">
-        <v>79881</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3816,38 +3816,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596183</v>
+        <v>596178</v>
       </c>
       <c r="R32" t="n">
-        <v>7033741</v>
+        <v>7033743</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3906,10 +3910,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255552</v>
+        <v>123255954</v>
       </c>
       <c r="B33" t="n">
-        <v>90957</v>
+        <v>91250</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3922,21 +3926,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3946,10 +3950,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596192</v>
+        <v>596185</v>
       </c>
       <c r="R33" t="n">
-        <v>7033765</v>
+        <v>7033739</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4008,10 +4012,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123256126</v>
+        <v>123255986</v>
       </c>
       <c r="B34" t="n">
-        <v>90957</v>
+        <v>79882</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,25 +4024,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4048,10 +4052,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596202</v>
+        <v>596183</v>
       </c>
       <c r="R34" t="n">
-        <v>7033790</v>
+        <v>7033741</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4110,10 +4114,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123253931</v>
+        <v>123256408</v>
       </c>
       <c r="B35" t="n">
-        <v>79852</v>
+        <v>90963</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4126,21 +4130,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4150,10 +4154,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596135</v>
+        <v>596171</v>
       </c>
       <c r="R35" t="n">
-        <v>7033851</v>
+        <v>7033849</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4212,10 +4216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123255893</v>
+        <v>123255199</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4247,7 +4251,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4256,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596178</v>
+        <v>596170</v>
       </c>
       <c r="R36" t="n">
-        <v>7033743</v>
+        <v>7033820</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4318,10 +4322,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123255199</v>
+        <v>123255552</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4330,42 +4334,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596170</v>
+        <v>596192</v>
       </c>
       <c r="R37" t="n">
-        <v>7033820</v>
+        <v>7033765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123255234</v>
+        <v>123256248</v>
       </c>
       <c r="B38" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596160</v>
+        <v>596180</v>
       </c>
       <c r="R38" t="n">
-        <v>7033817</v>
+        <v>7033809</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4530,10 +4530,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123255954</v>
+        <v>123256126</v>
       </c>
       <c r="B39" t="n">
-        <v>91244</v>
+        <v>90963</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4546,21 +4546,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596185</v>
+        <v>596202</v>
       </c>
       <c r="R39" t="n">
-        <v>7033739</v>
+        <v>7033790</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123256408</v>
+        <v>123254018</v>
       </c>
       <c r="B40" t="n">
-        <v>90957</v>
+        <v>79853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4648,21 +4648,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596171</v>
+        <v>596115</v>
       </c>
       <c r="R40" t="n">
-        <v>7033849</v>
+        <v>7033816</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4734,10 +4734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123254018</v>
+        <v>123253931</v>
       </c>
       <c r="B41" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596115</v>
+        <v>596135</v>
       </c>
       <c r="R41" t="n">
-        <v>7033816</v>
+        <v>7033851</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123255986</v>
+        <v>123255552</v>
       </c>
       <c r="B31" t="n">
-        <v>79885</v>
+        <v>90983</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,25 +3710,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596183</v>
+        <v>596192</v>
       </c>
       <c r="R31" t="n">
-        <v>7033741</v>
+        <v>7033765</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123254018</v>
+        <v>123255234</v>
       </c>
       <c r="B32" t="n">
-        <v>79856</v>
+        <v>98396</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,38 +3812,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596115</v>
+        <v>596160</v>
       </c>
       <c r="R32" t="n">
-        <v>7033816</v>
+        <v>7033817</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3902,10 +3906,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123256408</v>
+        <v>123255893</v>
       </c>
       <c r="B33" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,38 +3918,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596171</v>
+        <v>596178</v>
       </c>
       <c r="R33" t="n">
-        <v>7033849</v>
+        <v>7033743</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4004,10 +4012,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123256248</v>
+        <v>123256126</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4016,42 +4024,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596180</v>
+        <v>596202</v>
       </c>
       <c r="R34" t="n">
-        <v>7033809</v>
+        <v>7033790</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4110,10 +4114,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123255234</v>
+        <v>123255986</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4122,42 +4126,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596160</v>
+        <v>596183</v>
       </c>
       <c r="R35" t="n">
-        <v>7033817</v>
+        <v>7033741</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4216,10 +4216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123255199</v>
+        <v>123256248</v>
       </c>
       <c r="B36" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596170</v>
+        <v>596180</v>
       </c>
       <c r="R36" t="n">
-        <v>7033820</v>
+        <v>7033809</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4322,10 +4322,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123256126</v>
+        <v>123256408</v>
       </c>
       <c r="B37" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596202</v>
+        <v>596171</v>
       </c>
       <c r="R37" t="n">
-        <v>7033790</v>
+        <v>7033849</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123253931</v>
+        <v>123255199</v>
       </c>
       <c r="B38" t="n">
-        <v>79856</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4436,38 +4436,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596135</v>
+        <v>596170</v>
       </c>
       <c r="R38" t="n">
-        <v>7033851</v>
+        <v>7033820</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4529,7 +4533,7 @@
         <v>123255954</v>
       </c>
       <c r="B39" t="n">
-        <v>91253</v>
+        <v>91270</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4628,10 +4632,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123255552</v>
+        <v>123253931</v>
       </c>
       <c r="B40" t="n">
-        <v>90966</v>
+        <v>79862</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4644,21 +4648,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4668,10 +4672,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596192</v>
+        <v>596135</v>
       </c>
       <c r="R40" t="n">
-        <v>7033765</v>
+        <v>7033851</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4730,10 +4734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123255893</v>
+        <v>123254018</v>
       </c>
       <c r="B41" t="n">
-        <v>98379</v>
+        <v>79862</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4742,42 +4746,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596178</v>
+        <v>596115</v>
       </c>
       <c r="R41" t="n">
-        <v>7033743</v>
+        <v>7033816</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3906,10 +3906,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255893</v>
+        <v>123256126</v>
       </c>
       <c r="B33" t="n">
-        <v>98396</v>
+        <v>90983</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3918,42 +3918,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596178</v>
+        <v>596202</v>
       </c>
       <c r="R33" t="n">
-        <v>7033743</v>
+        <v>7033790</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4012,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123256126</v>
+        <v>123255893</v>
       </c>
       <c r="B34" t="n">
-        <v>90983</v>
+        <v>98396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4024,38 +4020,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596202</v>
+        <v>596178</v>
       </c>
       <c r="R34" t="n">
-        <v>7033790</v>
+        <v>7033743</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123255552</v>
+        <v>123255954</v>
       </c>
       <c r="B31" t="n">
-        <v>90983</v>
+        <v>91275</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596192</v>
+        <v>596185</v>
       </c>
       <c r="R31" t="n">
-        <v>7033765</v>
+        <v>7033739</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123255234</v>
+        <v>123255986</v>
       </c>
       <c r="B32" t="n">
-        <v>98396</v>
+        <v>79896</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,42 +3812,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596160</v>
+        <v>596183</v>
       </c>
       <c r="R32" t="n">
-        <v>7033817</v>
+        <v>7033741</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3906,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123256126</v>
+        <v>123255552</v>
       </c>
       <c r="B33" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3946,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596202</v>
+        <v>596192</v>
       </c>
       <c r="R33" t="n">
-        <v>7033790</v>
+        <v>7033765</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4008,10 +4004,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123255893</v>
+        <v>123256408</v>
       </c>
       <c r="B34" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,42 +4016,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596178</v>
+        <v>596171</v>
       </c>
       <c r="R34" t="n">
-        <v>7033743</v>
+        <v>7033849</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4114,10 +4106,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123255986</v>
+        <v>123255234</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>98502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4126,38 +4118,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596183</v>
+        <v>596160</v>
       </c>
       <c r="R35" t="n">
-        <v>7033741</v>
+        <v>7033817</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4216,10 +4212,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123256248</v>
+        <v>123255199</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4251,7 +4247,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4260,10 +4256,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596180</v>
+        <v>596170</v>
       </c>
       <c r="R36" t="n">
-        <v>7033809</v>
+        <v>7033820</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4322,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123256408</v>
+        <v>123254018</v>
       </c>
       <c r="B37" t="n">
-        <v>90983</v>
+        <v>79867</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4338,21 +4334,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4362,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596171</v>
+        <v>596115</v>
       </c>
       <c r="R37" t="n">
-        <v>7033849</v>
+        <v>7033816</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4424,10 +4420,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123255199</v>
+        <v>123255893</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,7 +4455,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4468,10 +4464,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596170</v>
+        <v>596178</v>
       </c>
       <c r="R38" t="n">
-        <v>7033820</v>
+        <v>7033743</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4530,10 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123255954</v>
+        <v>123256248</v>
       </c>
       <c r="B39" t="n">
-        <v>91270</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4542,38 +4538,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596185</v>
+        <v>596180</v>
       </c>
       <c r="R39" t="n">
-        <v>7033739</v>
+        <v>7033809</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4635,7 +4635,7 @@
         <v>123253931</v>
       </c>
       <c r="B40" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4734,10 +4734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123254018</v>
+        <v>123256126</v>
       </c>
       <c r="B41" t="n">
-        <v>79862</v>
+        <v>90988</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4750,21 +4750,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596115</v>
+        <v>596202</v>
       </c>
       <c r="R41" t="n">
-        <v>7033816</v>
+        <v>7033790</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123255954</v>
+        <v>123256126</v>
       </c>
       <c r="B31" t="n">
-        <v>91275</v>
+        <v>90990</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596185</v>
+        <v>596202</v>
       </c>
       <c r="R31" t="n">
-        <v>7033739</v>
+        <v>7033790</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123255986</v>
+        <v>123255954</v>
       </c>
       <c r="B32" t="n">
-        <v>79896</v>
+        <v>91277</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596183</v>
+        <v>596185</v>
       </c>
       <c r="R32" t="n">
-        <v>7033741</v>
+        <v>7033739</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255552</v>
+        <v>123255199</v>
       </c>
       <c r="B33" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,38 +3914,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596192</v>
+        <v>596170</v>
       </c>
       <c r="R33" t="n">
-        <v>7033765</v>
+        <v>7033820</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4004,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123256408</v>
+        <v>123254018</v>
       </c>
       <c r="B34" t="n">
-        <v>90988</v>
+        <v>79869</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,21 +4024,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4044,10 +4048,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596171</v>
+        <v>596115</v>
       </c>
       <c r="R34" t="n">
-        <v>7033849</v>
+        <v>7033816</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4106,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123255234</v>
+        <v>123255893</v>
       </c>
       <c r="B35" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4141,7 +4145,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4150,10 +4154,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596160</v>
+        <v>596178</v>
       </c>
       <c r="R35" t="n">
-        <v>7033817</v>
+        <v>7033743</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4212,10 +4216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123255199</v>
+        <v>123255986</v>
       </c>
       <c r="B36" t="n">
-        <v>98502</v>
+        <v>79898</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4224,42 +4228,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596170</v>
+        <v>596183</v>
       </c>
       <c r="R36" t="n">
-        <v>7033820</v>
+        <v>7033741</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4318,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123254018</v>
+        <v>123255552</v>
       </c>
       <c r="B37" t="n">
-        <v>79867</v>
+        <v>90990</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4334,21 +4334,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596115</v>
+        <v>596192</v>
       </c>
       <c r="R37" t="n">
-        <v>7033816</v>
+        <v>7033765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123255893</v>
+        <v>123253931</v>
       </c>
       <c r="B38" t="n">
-        <v>98502</v>
+        <v>79869</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4432,42 +4432,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596178</v>
+        <v>596135</v>
       </c>
       <c r="R38" t="n">
-        <v>7033743</v>
+        <v>7033851</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4529,7 +4525,7 @@
         <v>123256248</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4632,10 +4628,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123253931</v>
+        <v>123255234</v>
       </c>
       <c r="B40" t="n">
-        <v>79867</v>
+        <v>98504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4644,38 +4640,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596135</v>
+        <v>596160</v>
       </c>
       <c r="R40" t="n">
-        <v>7033851</v>
+        <v>7033817</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4734,10 +4734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123256126</v>
+        <v>123256408</v>
       </c>
       <c r="B41" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596202</v>
+        <v>596171</v>
       </c>
       <c r="R41" t="n">
-        <v>7033790</v>
+        <v>7033849</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,7 +3698,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123256126</v>
+        <v>123256408</v>
       </c>
       <c r="B31" t="n">
         <v>90990</v>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596202</v>
+        <v>596171</v>
       </c>
       <c r="R31" t="n">
-        <v>7033790</v>
+        <v>7033849</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123255954</v>
+        <v>123255986</v>
       </c>
       <c r="B32" t="n">
-        <v>91277</v>
+        <v>79898</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596185</v>
+        <v>596183</v>
       </c>
       <c r="R32" t="n">
-        <v>7033739</v>
+        <v>7033741</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255199</v>
+        <v>123255234</v>
       </c>
       <c r="B33" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596170</v>
+        <v>596160</v>
       </c>
       <c r="R33" t="n">
-        <v>7033820</v>
+        <v>7033817</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4008,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123254018</v>
+        <v>123255954</v>
       </c>
       <c r="B34" t="n">
-        <v>79869</v>
+        <v>91277</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596115</v>
+        <v>596185</v>
       </c>
       <c r="R34" t="n">
-        <v>7033816</v>
+        <v>7033739</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123255893</v>
+        <v>123255199</v>
       </c>
       <c r="B35" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596178</v>
+        <v>596170</v>
       </c>
       <c r="R35" t="n">
-        <v>7033743</v>
+        <v>7033820</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4216,10 +4216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123255986</v>
+        <v>123253931</v>
       </c>
       <c r="B36" t="n">
-        <v>79898</v>
+        <v>79869</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,25 +4228,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596183</v>
+        <v>596135</v>
       </c>
       <c r="R36" t="n">
-        <v>7033741</v>
+        <v>7033851</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4318,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123255552</v>
+        <v>123256248</v>
       </c>
       <c r="B37" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4330,38 +4330,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596192</v>
+        <v>596180</v>
       </c>
       <c r="R37" t="n">
-        <v>7033765</v>
+        <v>7033809</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4420,10 +4424,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123253931</v>
+        <v>123256126</v>
       </c>
       <c r="B38" t="n">
-        <v>79869</v>
+        <v>90990</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4436,21 +4440,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4460,10 +4464,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596135</v>
+        <v>596202</v>
       </c>
       <c r="R38" t="n">
-        <v>7033851</v>
+        <v>7033790</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4522,10 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123256248</v>
+        <v>123255893</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4557,7 +4561,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4566,10 +4570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596180</v>
+        <v>596178</v>
       </c>
       <c r="R39" t="n">
-        <v>7033809</v>
+        <v>7033743</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4628,10 +4632,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123255234</v>
+        <v>123254018</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>79869</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4640,42 +4644,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596160</v>
+        <v>596115</v>
       </c>
       <c r="R40" t="n">
-        <v>7033817</v>
+        <v>7033816</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123256408</v>
+        <v>123255552</v>
       </c>
       <c r="B41" t="n">
         <v>90990</v>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596171</v>
+        <v>596192</v>
       </c>
       <c r="R41" t="n">
-        <v>7033849</v>
+        <v>7033765</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4526,10 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123255893</v>
+        <v>123254018</v>
       </c>
       <c r="B39" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4538,42 +4538,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596178</v>
+        <v>596115</v>
       </c>
       <c r="R39" t="n">
-        <v>7033743</v>
+        <v>7033816</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,10 +4628,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123254018</v>
+        <v>123255893</v>
       </c>
       <c r="B40" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4644,38 +4640,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596115</v>
+        <v>596178</v>
       </c>
       <c r="R40" t="n">
-        <v>7033816</v>
+        <v>7033743</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123256408</v>
+        <v>123255199</v>
       </c>
       <c r="B31" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,38 +3710,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596171</v>
+        <v>596170</v>
       </c>
       <c r="R31" t="n">
-        <v>7033849</v>
+        <v>7033820</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3800,10 +3804,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123255986</v>
+        <v>123255234</v>
       </c>
       <c r="B32" t="n">
-        <v>79898</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,38 +3816,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596183</v>
+        <v>596160</v>
       </c>
       <c r="R32" t="n">
-        <v>7033741</v>
+        <v>7033817</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3902,10 +3910,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255234</v>
+        <v>123255954</v>
       </c>
       <c r="B33" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,42 +3922,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596160</v>
+        <v>596185</v>
       </c>
       <c r="R33" t="n">
-        <v>7033817</v>
+        <v>7033739</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4008,10 +4012,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123255954</v>
+        <v>123255893</v>
       </c>
       <c r="B34" t="n">
-        <v>91277</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,38 +4024,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596185</v>
+        <v>596178</v>
       </c>
       <c r="R34" t="n">
-        <v>7033739</v>
+        <v>7033743</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4110,10 +4118,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123255199</v>
+        <v>123256408</v>
       </c>
       <c r="B35" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4122,42 +4130,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596170</v>
+        <v>596171</v>
       </c>
       <c r="R35" t="n">
-        <v>7033820</v>
+        <v>7033849</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4216,10 +4220,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123253931</v>
+        <v>123255986</v>
       </c>
       <c r="B36" t="n">
-        <v>79869</v>
+        <v>79898</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,25 +4232,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4256,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596135</v>
+        <v>596183</v>
       </c>
       <c r="R36" t="n">
-        <v>7033851</v>
+        <v>7033741</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4318,10 +4322,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123256248</v>
+        <v>123254018</v>
       </c>
       <c r="B37" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4330,42 +4334,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596180</v>
+        <v>596115</v>
       </c>
       <c r="R37" t="n">
-        <v>7033809</v>
+        <v>7033816</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123254018</v>
+        <v>123255552</v>
       </c>
       <c r="B39" t="n">
-        <v>79869</v>
+        <v>90990</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4542,21 +4542,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596115</v>
+        <v>596192</v>
       </c>
       <c r="R39" t="n">
-        <v>7033816</v>
+        <v>7033765</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123255893</v>
+        <v>123256248</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596178</v>
+        <v>596180</v>
       </c>
       <c r="R40" t="n">
-        <v>7033743</v>
+        <v>7033809</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4734,10 +4734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123255552</v>
+        <v>123253931</v>
       </c>
       <c r="B41" t="n">
-        <v>90990</v>
+        <v>79869</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4750,21 +4750,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596192</v>
+        <v>596135</v>
       </c>
       <c r="R41" t="n">
-        <v>7033765</v>
+        <v>7033851</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4834,6 +4834,2056 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127376403</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>596203</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7033831</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127376010</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>596194</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7033844</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127377453</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>596164</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7033777</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127372251</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91621</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>658</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>596208</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7033752</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127375798</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91621</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>658</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>596193</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7033848</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127374649</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>596191</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7033805</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127375059</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>596149</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7033864</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127376909</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>596209</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7033789</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127372269</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>596207</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7033752</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127375195</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80153</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>596167</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7033854</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127377215</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>596190</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7033789</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127372260</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>596208</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7033752</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127375850</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>596183</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7033841</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127376674</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91290</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>596197</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7033813</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127375177</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>596172</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7033852</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127375927</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80145</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>596203</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7033839</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127375277</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>596162</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7033857</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127374492</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>596186</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7033816</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127375316</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80152</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>596161</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7033859</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127372611</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91290</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>596196</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7033769</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127374836</v>
+      </c>
+      <c r="B62" t="n">
+        <v>97320</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>596170</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7033847</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4839,7 +4839,7 @@
         <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4933,54 +4933,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127376010</v>
+        <v>127377453</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596194</v>
+        <v>596164</v>
       </c>
       <c r="R43" t="n">
-        <v>7033844</v>
+        <v>7033777</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5039,45 +5030,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127377453</v>
+        <v>127376010</v>
       </c>
       <c r="B44" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596164</v>
+        <v>596194</v>
       </c>
       <c r="R44" t="n">
-        <v>7033777</v>
+        <v>7033844</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5524,10 +5524,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127376909</v>
+        <v>127372269</v>
       </c>
       <c r="B49" t="n">
-        <v>91325</v>
+        <v>80117</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596209</v>
+        <v>596207</v>
       </c>
       <c r="R49" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127372269</v>
+        <v>127376909</v>
       </c>
       <c r="B50" t="n">
-        <v>80117</v>
+        <v>91326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596207</v>
+        <v>596209</v>
       </c>
       <c r="R50" t="n">
-        <v>7033752</v>
+        <v>7033789</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5815,49 +5815,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127377215</v>
+        <v>127375850</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596190</v>
+        <v>596183</v>
       </c>
       <c r="R52" t="n">
-        <v>7033789</v>
+        <v>7033841</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5919,7 +5915,7 @@
         <v>127372260</v>
       </c>
       <c r="B53" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6013,45 +6009,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127375850</v>
+        <v>127377215</v>
       </c>
       <c r="B54" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596183</v>
+        <v>596190</v>
       </c>
       <c r="R54" t="n">
-        <v>7033841</v>
+        <v>7033789</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375059</v>
+        <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>91326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596149</v>
+        <v>596209</v>
       </c>
       <c r="R48" t="n">
-        <v>7033864</v>
+        <v>7033789</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127372269</v>
+        <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596207</v>
+        <v>596149</v>
       </c>
       <c r="R49" t="n">
-        <v>7033752</v>
+        <v>7033864</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127376909</v>
+        <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>91326</v>
+        <v>80117</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596209</v>
+        <v>596207</v>
       </c>
       <c r="R50" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5718,45 +5718,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B51" t="n">
-        <v>80153</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R51" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,7 +5819,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375850</v>
+        <v>127372260</v>
       </c>
       <c r="B52" t="n">
         <v>91326</v>
@@ -5850,10 +5854,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596183</v>
+        <v>596208</v>
       </c>
       <c r="R52" t="n">
-        <v>7033841</v>
+        <v>7033752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,7 +5916,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B53" t="n">
         <v>91326</v>
@@ -5947,10 +5951,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R53" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6009,49 +6013,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127377215</v>
+        <v>127375195</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>80153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596190</v>
+        <v>596167</v>
       </c>
       <c r="R54" t="n">
-        <v>7033789</v>
+        <v>7033854</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5718,49 +5718,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127377215</v>
+        <v>127372260</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596190</v>
+        <v>596208</v>
       </c>
       <c r="R51" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5819,7 +5815,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B52" t="n">
         <v>91326</v>
@@ -5854,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R52" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5916,45 +5912,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375850</v>
+        <v>127377215</v>
       </c>
       <c r="B53" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596183</v>
+        <v>596190</v>
       </c>
       <c r="R53" t="n">
-        <v>7033841</v>
+        <v>7033789</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5718,45 +5718,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127372260</v>
+        <v>127377215</v>
       </c>
       <c r="B51" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596208</v>
+        <v>596190</v>
       </c>
       <c r="R51" t="n">
-        <v>7033752</v>
+        <v>7033789</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,7 +5819,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375850</v>
+        <v>127372260</v>
       </c>
       <c r="B52" t="n">
         <v>91326</v>
@@ -5850,10 +5854,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596183</v>
+        <v>596208</v>
       </c>
       <c r="R52" t="n">
-        <v>7033841</v>
+        <v>7033752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,49 +5916,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127377215</v>
+        <v>127375850</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596190</v>
+        <v>596183</v>
       </c>
       <c r="R53" t="n">
-        <v>7033789</v>
+        <v>7033841</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4839,7 +4839,7 @@
         <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>127377453</v>
       </c>
       <c r="B43" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>127376010</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5718,49 +5718,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127377215</v>
+        <v>127375850</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596190</v>
+        <v>596183</v>
       </c>
       <c r="R51" t="n">
-        <v>7033789</v>
+        <v>7033841</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5822,7 +5818,7 @@
         <v>127372260</v>
       </c>
       <c r="B52" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5916,32 +5912,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375850</v>
+        <v>127375195</v>
       </c>
       <c r="B53" t="n">
-        <v>91326</v>
+        <v>80157</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5951,10 +5947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596183</v>
+        <v>596167</v>
       </c>
       <c r="R53" t="n">
-        <v>7033841</v>
+        <v>7033854</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6013,45 +6009,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B54" t="n">
-        <v>80153</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R54" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6207,32 +6207,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127375177</v>
+        <v>127375927</v>
       </c>
       <c r="B56" t="n">
-        <v>80117</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596172</v>
+        <v>596203</v>
       </c>
       <c r="R56" t="n">
-        <v>7033852</v>
+        <v>7033839</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6304,32 +6304,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127375927</v>
+        <v>127375177</v>
       </c>
       <c r="B57" t="n">
-        <v>80145</v>
+        <v>80121</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596203</v>
+        <v>596172</v>
       </c>
       <c r="R57" t="n">
-        <v>7033839</v>
+        <v>7033852</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6404,7 +6404,7 @@
         <v>127375277</v>
       </c>
       <c r="B58" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>127375316</v>
       </c>
       <c r="B60" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4836,7 +4836,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127376403</v>
+        <v>127377453</v>
       </c>
       <c r="B42" t="n">
         <v>91330</v>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596203</v>
+        <v>596164</v>
       </c>
       <c r="R42" t="n">
-        <v>7033831</v>
+        <v>7033777</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4933,45 +4933,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127377453</v>
+        <v>127376010</v>
       </c>
       <c r="B43" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596164</v>
+        <v>596194</v>
       </c>
       <c r="R43" t="n">
-        <v>7033777</v>
+        <v>7033844</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5030,54 +5039,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127376010</v>
+        <v>127376403</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596194</v>
+        <v>596203</v>
       </c>
       <c r="R44" t="n">
-        <v>7033844</v>
+        <v>7033831</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127376909</v>
+        <v>127375059</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596209</v>
+        <v>596149</v>
       </c>
       <c r="R48" t="n">
-        <v>7033789</v>
+        <v>7033864</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375059</v>
+        <v>127372269</v>
       </c>
       <c r="B49" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596149</v>
+        <v>596207</v>
       </c>
       <c r="R49" t="n">
-        <v>7033864</v>
+        <v>7033752</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127372269</v>
+        <v>127376909</v>
       </c>
       <c r="B50" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596207</v>
+        <v>596209</v>
       </c>
       <c r="R50" t="n">
-        <v>7033752</v>
+        <v>7033789</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5912,45 +5912,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B53" t="n">
-        <v>80157</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R53" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6009,49 +6013,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127377215</v>
+        <v>127375195</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>80157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596190</v>
+        <v>596167</v>
       </c>
       <c r="R54" t="n">
-        <v>7033789</v>
+        <v>7033854</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6207,32 +6207,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127375927</v>
+        <v>127375177</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>80121</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596203</v>
+        <v>596172</v>
       </c>
       <c r="R56" t="n">
-        <v>7033839</v>
+        <v>7033852</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6304,32 +6304,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127375177</v>
+        <v>127375927</v>
       </c>
       <c r="B57" t="n">
-        <v>80121</v>
+        <v>80149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596172</v>
+        <v>596203</v>
       </c>
       <c r="R57" t="n">
-        <v>7033852</v>
+        <v>7033839</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375059</v>
+        <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>80150</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596149</v>
+        <v>596209</v>
       </c>
       <c r="R48" t="n">
-        <v>7033864</v>
+        <v>7033789</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127372269</v>
+        <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80121</v>
+        <v>80150</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596207</v>
+        <v>596149</v>
       </c>
       <c r="R49" t="n">
-        <v>7033752</v>
+        <v>7033864</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127376909</v>
+        <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596209</v>
+        <v>596207</v>
       </c>
       <c r="R50" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127376909</v>
+        <v>127375059</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596209</v>
+        <v>596149</v>
       </c>
       <c r="R48" t="n">
-        <v>7033789</v>
+        <v>7033864</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375059</v>
+        <v>127372269</v>
       </c>
       <c r="B49" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596149</v>
+        <v>596207</v>
       </c>
       <c r="R49" t="n">
-        <v>7033864</v>
+        <v>7033752</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127372269</v>
+        <v>127376909</v>
       </c>
       <c r="B50" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596207</v>
+        <v>596209</v>
       </c>
       <c r="R50" t="n">
-        <v>7033752</v>
+        <v>7033789</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4836,45 +4836,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127377453</v>
+        <v>127376010</v>
       </c>
       <c r="B42" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596164</v>
+        <v>596194</v>
       </c>
       <c r="R42" t="n">
-        <v>7033777</v>
+        <v>7033844</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4933,54 +4942,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127376010</v>
+        <v>127376403</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596194</v>
+        <v>596203</v>
       </c>
       <c r="R43" t="n">
-        <v>7033844</v>
+        <v>7033831</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5039,7 +5039,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127376403</v>
+        <v>127377453</v>
       </c>
       <c r="B44" t="n">
         <v>91330</v>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596203</v>
+        <v>596164</v>
       </c>
       <c r="R44" t="n">
-        <v>7033831</v>
+        <v>7033777</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375059</v>
+        <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>80150</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596149</v>
+        <v>596209</v>
       </c>
       <c r="R48" t="n">
-        <v>7033864</v>
+        <v>7033789</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127372269</v>
+        <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80121</v>
+        <v>80150</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596207</v>
+        <v>596149</v>
       </c>
       <c r="R49" t="n">
-        <v>7033752</v>
+        <v>7033864</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127376909</v>
+        <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596209</v>
+        <v>596207</v>
       </c>
       <c r="R50" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5718,45 +5718,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375850</v>
+        <v>127377215</v>
       </c>
       <c r="B51" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596183</v>
+        <v>596190</v>
       </c>
       <c r="R51" t="n">
-        <v>7033841</v>
+        <v>7033789</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,7 +5819,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B52" t="n">
         <v>91330</v>
@@ -5850,10 +5854,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R52" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,49 +5916,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127377215</v>
+        <v>127372260</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596190</v>
+        <v>596208</v>
       </c>
       <c r="R53" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4836,54 +4836,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127376010</v>
+        <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596194</v>
+        <v>596203</v>
       </c>
       <c r="R42" t="n">
-        <v>7033844</v>
+        <v>7033831</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4942,7 +4933,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127376403</v>
+        <v>127377453</v>
       </c>
       <c r="B43" t="n">
         <v>91330</v>
@@ -4977,10 +4968,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596203</v>
+        <v>596164</v>
       </c>
       <c r="R43" t="n">
-        <v>7033831</v>
+        <v>7033777</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5039,45 +5030,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127377453</v>
+        <v>127376010</v>
       </c>
       <c r="B44" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596164</v>
+        <v>596194</v>
       </c>
       <c r="R44" t="n">
-        <v>7033777</v>
+        <v>7033844</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4839,7 +4839,7 @@
         <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>127377453</v>
       </c>
       <c r="B43" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>127376010</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5718,49 +5718,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127377215</v>
+        <v>127375850</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596190</v>
+        <v>596183</v>
       </c>
       <c r="R51" t="n">
-        <v>7033789</v>
+        <v>7033841</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5819,10 +5815,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375850</v>
+        <v>127372260</v>
       </c>
       <c r="B52" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5854,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596183</v>
+        <v>596208</v>
       </c>
       <c r="R52" t="n">
-        <v>7033841</v>
+        <v>7033752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5916,32 +5912,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127372260</v>
+        <v>127375195</v>
       </c>
       <c r="B53" t="n">
-        <v>91330</v>
+        <v>80159</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5951,10 +5947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596208</v>
+        <v>596167</v>
       </c>
       <c r="R53" t="n">
-        <v>7033752</v>
+        <v>7033854</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6013,45 +6009,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B54" t="n">
-        <v>80157</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R54" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>127375177</v>
       </c>
       <c r="B56" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>127375927</v>
       </c>
       <c r="B57" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>127375277</v>
       </c>
       <c r="B58" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>127375316</v>
       </c>
       <c r="B60" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5718,7 +5718,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375850</v>
+        <v>127372260</v>
       </c>
       <c r="B51" t="n">
         <v>91332</v>
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596183</v>
+        <v>596208</v>
       </c>
       <c r="R51" t="n">
-        <v>7033841</v>
+        <v>7033752</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,7 +5815,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B52" t="n">
         <v>91332</v>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R52" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6207,32 +6207,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127375177</v>
+        <v>127375927</v>
       </c>
       <c r="B56" t="n">
-        <v>80123</v>
+        <v>80151</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596172</v>
+        <v>596203</v>
       </c>
       <c r="R56" t="n">
-        <v>7033852</v>
+        <v>7033839</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6304,32 +6304,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127375927</v>
+        <v>127375177</v>
       </c>
       <c r="B57" t="n">
-        <v>80151</v>
+        <v>80123</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596203</v>
+        <v>596172</v>
       </c>
       <c r="R57" t="n">
-        <v>7033839</v>
+        <v>7033852</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5718,45 +5718,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127372260</v>
+        <v>127377215</v>
       </c>
       <c r="B51" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596208</v>
+        <v>596190</v>
       </c>
       <c r="R51" t="n">
-        <v>7033752</v>
+        <v>7033789</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,7 +5819,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375850</v>
+        <v>127372260</v>
       </c>
       <c r="B52" t="n">
         <v>91332</v>
@@ -5850,10 +5854,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596183</v>
+        <v>596208</v>
       </c>
       <c r="R52" t="n">
-        <v>7033841</v>
+        <v>7033752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,32 +5916,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375195</v>
+        <v>127375850</v>
       </c>
       <c r="B53" t="n">
-        <v>80159</v>
+        <v>91332</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5947,10 +5951,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596167</v>
+        <v>596183</v>
       </c>
       <c r="R53" t="n">
-        <v>7033854</v>
+        <v>7033841</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6009,49 +6013,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127377215</v>
+        <v>127375195</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>80159</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596190</v>
+        <v>596167</v>
       </c>
       <c r="R54" t="n">
-        <v>7033789</v>
+        <v>7033854</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127376909</v>
+        <v>127375059</v>
       </c>
       <c r="B48" t="n">
-        <v>91332</v>
+        <v>80152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596209</v>
+        <v>596149</v>
       </c>
       <c r="R48" t="n">
-        <v>7033789</v>
+        <v>7033864</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375059</v>
+        <v>127372269</v>
       </c>
       <c r="B49" t="n">
-        <v>80152</v>
+        <v>80123</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596149</v>
+        <v>596207</v>
       </c>
       <c r="R49" t="n">
-        <v>7033864</v>
+        <v>7033752</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127372269</v>
+        <v>127376909</v>
       </c>
       <c r="B50" t="n">
-        <v>80123</v>
+        <v>91332</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596207</v>
+        <v>596209</v>
       </c>
       <c r="R50" t="n">
-        <v>7033752</v>
+        <v>7033789</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5718,49 +5718,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127377215</v>
+        <v>127372260</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596190</v>
+        <v>596208</v>
       </c>
       <c r="R51" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5819,7 +5815,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B52" t="n">
         <v>91332</v>
@@ -5854,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R52" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5916,32 +5912,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375850</v>
+        <v>127375195</v>
       </c>
       <c r="B53" t="n">
-        <v>91332</v>
+        <v>80159</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5951,10 +5947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596183</v>
+        <v>596167</v>
       </c>
       <c r="R53" t="n">
-        <v>7033841</v>
+        <v>7033854</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6013,45 +6009,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B54" t="n">
-        <v>80159</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R54" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6207,32 +6207,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127375927</v>
+        <v>127375177</v>
       </c>
       <c r="B56" t="n">
-        <v>80151</v>
+        <v>80123</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596203</v>
+        <v>596172</v>
       </c>
       <c r="R56" t="n">
-        <v>7033839</v>
+        <v>7033852</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6304,32 +6304,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127375177</v>
+        <v>127375927</v>
       </c>
       <c r="B57" t="n">
-        <v>80123</v>
+        <v>80151</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596172</v>
+        <v>596203</v>
       </c>
       <c r="R57" t="n">
-        <v>7033852</v>
+        <v>7033839</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4839,7 +4839,7 @@
         <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>127377453</v>
       </c>
       <c r="B43" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>127376010</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375059</v>
+        <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>80152</v>
+        <v>91338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596149</v>
+        <v>596209</v>
       </c>
       <c r="R48" t="n">
-        <v>7033864</v>
+        <v>7033789</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127372269</v>
+        <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80123</v>
+        <v>80152</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596207</v>
+        <v>596149</v>
       </c>
       <c r="R49" t="n">
-        <v>7033752</v>
+        <v>7033864</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127376909</v>
+        <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596209</v>
+        <v>596207</v>
       </c>
       <c r="R50" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5718,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B51" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R51" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,10 +5815,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375850</v>
+        <v>127372260</v>
       </c>
       <c r="B52" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596183</v>
+        <v>596208</v>
       </c>
       <c r="R52" t="n">
-        <v>7033841</v>
+        <v>7033752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,45 +5912,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B53" t="n">
-        <v>80159</v>
+        <v>98456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R53" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6009,49 +6013,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127377215</v>
+        <v>127375195</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>80159</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596190</v>
+        <v>596167</v>
       </c>
       <c r="R54" t="n">
-        <v>7033789</v>
+        <v>7033854</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4836,45 +4836,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127376403</v>
+        <v>127376010</v>
       </c>
       <c r="B42" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596203</v>
+        <v>596194</v>
       </c>
       <c r="R42" t="n">
-        <v>7033831</v>
+        <v>7033844</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4933,10 +4942,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127377453</v>
+        <v>127376403</v>
       </c>
       <c r="B43" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,10 +4977,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596164</v>
+        <v>596203</v>
       </c>
       <c r="R43" t="n">
-        <v>7033777</v>
+        <v>7033831</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5030,54 +5039,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127376010</v>
+        <v>127377453</v>
       </c>
       <c r="B44" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596194</v>
+        <v>596164</v>
       </c>
       <c r="R44" t="n">
-        <v>7033844</v>
+        <v>7033777</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5718,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375850</v>
+        <v>127372260</v>
       </c>
       <c r="B51" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596183</v>
+        <v>596208</v>
       </c>
       <c r="R51" t="n">
-        <v>7033841</v>
+        <v>7033752</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,32 +5815,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127372260</v>
+        <v>127375195</v>
       </c>
       <c r="B52" t="n">
-        <v>91338</v>
+        <v>80162</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596208</v>
+        <v>596167</v>
       </c>
       <c r="R52" t="n">
-        <v>7033752</v>
+        <v>7033854</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,49 +5912,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127377215</v>
+        <v>127375850</v>
       </c>
       <c r="B53" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596190</v>
+        <v>596183</v>
       </c>
       <c r="R53" t="n">
-        <v>7033789</v>
+        <v>7033841</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6013,45 +6009,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B54" t="n">
-        <v>80159</v>
+        <v>98459</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R54" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>127375177</v>
       </c>
       <c r="B56" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>127375927</v>
       </c>
       <c r="B57" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>127375277</v>
       </c>
       <c r="B58" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>127375316</v>
       </c>
       <c r="B60" t="n">
-        <v>80158</v>
+        <v>80161</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4836,54 +4836,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127376010</v>
+        <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596194</v>
+        <v>596203</v>
       </c>
       <c r="R42" t="n">
-        <v>7033844</v>
+        <v>7033831</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4942,10 +4933,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127376403</v>
+        <v>127377453</v>
       </c>
       <c r="B43" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4977,10 +4968,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596203</v>
+        <v>596164</v>
       </c>
       <c r="R43" t="n">
-        <v>7033831</v>
+        <v>7033777</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5039,45 +5030,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127377453</v>
+        <v>127376010</v>
       </c>
       <c r="B44" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596164</v>
+        <v>596194</v>
       </c>
       <c r="R44" t="n">
-        <v>7033777</v>
+        <v>7033844</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5718,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B51" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R51" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,32 +5815,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375195</v>
+        <v>127372260</v>
       </c>
       <c r="B52" t="n">
-        <v>80162</v>
+        <v>91349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596167</v>
+        <v>596208</v>
       </c>
       <c r="R52" t="n">
-        <v>7033854</v>
+        <v>7033752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,45 +5912,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375850</v>
+        <v>127377215</v>
       </c>
       <c r="B53" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596183</v>
+        <v>596190</v>
       </c>
       <c r="R53" t="n">
-        <v>7033841</v>
+        <v>7033789</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6009,49 +6013,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127377215</v>
+        <v>127375195</v>
       </c>
       <c r="B54" t="n">
-        <v>98459</v>
+        <v>80168</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596190</v>
+        <v>596167</v>
       </c>
       <c r="R54" t="n">
-        <v>7033789</v>
+        <v>7033854</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>127375177</v>
       </c>
       <c r="B56" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>127375927</v>
       </c>
       <c r="B57" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>127375277</v>
       </c>
       <c r="B58" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>127375316</v>
       </c>
       <c r="B60" t="n">
-        <v>80161</v>
+        <v>80167</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4839,7 +4839,7 @@
         <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4933,45 +4933,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127377453</v>
+        <v>127376010</v>
       </c>
       <c r="B43" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596164</v>
+        <v>596194</v>
       </c>
       <c r="R43" t="n">
-        <v>7033777</v>
+        <v>7033844</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5030,54 +5039,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127376010</v>
+        <v>127377453</v>
       </c>
       <c r="B44" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596194</v>
+        <v>596164</v>
       </c>
       <c r="R44" t="n">
-        <v>7033844</v>
+        <v>7033777</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127376909</v>
+        <v>127375059</v>
       </c>
       <c r="B48" t="n">
-        <v>91349</v>
+        <v>80161</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596209</v>
+        <v>596149</v>
       </c>
       <c r="R48" t="n">
-        <v>7033789</v>
+        <v>7033864</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375059</v>
+        <v>127372269</v>
       </c>
       <c r="B49" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596149</v>
+        <v>596207</v>
       </c>
       <c r="R49" t="n">
-        <v>7033864</v>
+        <v>7033752</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127372269</v>
+        <v>127376909</v>
       </c>
       <c r="B50" t="n">
-        <v>80132</v>
+        <v>91350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596207</v>
+        <v>596209</v>
       </c>
       <c r="R50" t="n">
-        <v>7033752</v>
+        <v>7033789</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5721,7 +5721,7 @@
         <v>127375850</v>
       </c>
       <c r="B51" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127372260</v>
       </c>
       <c r="B52" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>127377215</v>
       </c>
       <c r="B53" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6207,32 +6207,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127375177</v>
+        <v>127375927</v>
       </c>
       <c r="B56" t="n">
-        <v>80132</v>
+        <v>80160</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596172</v>
+        <v>596203</v>
       </c>
       <c r="R56" t="n">
-        <v>7033852</v>
+        <v>7033839</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6304,32 +6304,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127375927</v>
+        <v>127375177</v>
       </c>
       <c r="B57" t="n">
-        <v>80160</v>
+        <v>80132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596203</v>
+        <v>596172</v>
       </c>
       <c r="R57" t="n">
-        <v>7033839</v>
+        <v>7033852</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4836,45 +4836,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127376403</v>
+        <v>127376010</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>98468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596203</v>
+        <v>596194</v>
       </c>
       <c r="R42" t="n">
-        <v>7033831</v>
+        <v>7033844</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4933,54 +4942,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127376010</v>
+        <v>127376403</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>91350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596194</v>
+        <v>596203</v>
       </c>
       <c r="R43" t="n">
-        <v>7033844</v>
+        <v>7033831</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375059</v>
+        <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>80161</v>
+        <v>91350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596149</v>
+        <v>596209</v>
       </c>
       <c r="R48" t="n">
-        <v>7033864</v>
+        <v>7033789</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127372269</v>
+        <v>127375059</v>
       </c>
       <c r="B49" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596207</v>
+        <v>596149</v>
       </c>
       <c r="R49" t="n">
-        <v>7033752</v>
+        <v>7033864</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127376909</v>
+        <v>127372269</v>
       </c>
       <c r="B50" t="n">
-        <v>91350</v>
+        <v>80132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596209</v>
+        <v>596207</v>
       </c>
       <c r="R50" t="n">
-        <v>7033789</v>
+        <v>7033752</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5912,49 +5912,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127377215</v>
+        <v>127375195</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>80168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596190</v>
+        <v>596167</v>
       </c>
       <c r="R53" t="n">
-        <v>7033789</v>
+        <v>7033854</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6013,45 +6009,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B54" t="n">
-        <v>80168</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R54" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6207,32 +6207,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127375927</v>
+        <v>127375177</v>
       </c>
       <c r="B56" t="n">
-        <v>80160</v>
+        <v>80132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596203</v>
+        <v>596172</v>
       </c>
       <c r="R56" t="n">
-        <v>7033839</v>
+        <v>7033852</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6304,32 +6304,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127375177</v>
+        <v>127375927</v>
       </c>
       <c r="B57" t="n">
-        <v>80132</v>
+        <v>80160</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596172</v>
+        <v>596203</v>
       </c>
       <c r="R57" t="n">
-        <v>7033852</v>
+        <v>7033839</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4836,54 +4836,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127376010</v>
+        <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>98468</v>
+        <v>91351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596194</v>
+        <v>596203</v>
       </c>
       <c r="R42" t="n">
-        <v>7033844</v>
+        <v>7033831</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4942,10 +4933,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127376403</v>
+        <v>127377453</v>
       </c>
       <c r="B43" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4977,10 +4968,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596203</v>
+        <v>596164</v>
       </c>
       <c r="R43" t="n">
-        <v>7033831</v>
+        <v>7033777</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5039,45 +5030,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127377453</v>
+        <v>127376010</v>
       </c>
       <c r="B44" t="n">
-        <v>91350</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596164</v>
+        <v>596194</v>
       </c>
       <c r="R44" t="n">
-        <v>7033777</v>
+        <v>7033844</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5718,45 +5718,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375850</v>
+        <v>127377215</v>
       </c>
       <c r="B51" t="n">
-        <v>91350</v>
+        <v>98469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596183</v>
+        <v>596190</v>
       </c>
       <c r="R51" t="n">
-        <v>7033841</v>
+        <v>7033789</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,10 +5819,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B52" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5850,10 +5854,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R52" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,32 +5916,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375195</v>
+        <v>127372260</v>
       </c>
       <c r="B53" t="n">
-        <v>80168</v>
+        <v>91351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5947,10 +5951,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596167</v>
+        <v>596208</v>
       </c>
       <c r="R53" t="n">
-        <v>7033854</v>
+        <v>7033752</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6009,49 +6013,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127377215</v>
+        <v>127375195</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>80168</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596190</v>
+        <v>596167</v>
       </c>
       <c r="R54" t="n">
-        <v>7033789</v>
+        <v>7033854</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4839,7 +4839,7 @@
         <v>127376403</v>
       </c>
       <c r="B42" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>127377453</v>
       </c>
       <c r="B43" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>127376010</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>127372251</v>
       </c>
       <c r="B45" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>127375798</v>
       </c>
       <c r="B46" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>127374649</v>
       </c>
       <c r="B47" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>127376909</v>
       </c>
       <c r="B48" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5718,49 +5718,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127377215</v>
+        <v>127375850</v>
       </c>
       <c r="B51" t="n">
-        <v>98469</v>
+        <v>91352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596190</v>
+        <v>596183</v>
       </c>
       <c r="R51" t="n">
-        <v>7033789</v>
+        <v>7033841</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5819,10 +5815,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375850</v>
+        <v>127372260</v>
       </c>
       <c r="B52" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5854,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596183</v>
+        <v>596208</v>
       </c>
       <c r="R52" t="n">
-        <v>7033841</v>
+        <v>7033752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5916,32 +5912,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127372260</v>
+        <v>127375195</v>
       </c>
       <c r="B53" t="n">
-        <v>91351</v>
+        <v>80168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5951,10 +5947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596208</v>
+        <v>596167</v>
       </c>
       <c r="R53" t="n">
-        <v>7033752</v>
+        <v>7033854</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6013,45 +6009,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127375195</v>
+        <v>127377215</v>
       </c>
       <c r="B54" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596167</v>
+        <v>596190</v>
       </c>
       <c r="R54" t="n">
-        <v>7033854</v>
+        <v>7033789</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6113,7 +6113,7 @@
         <v>127376674</v>
       </c>
       <c r="B55" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>127374492</v>
       </c>
       <c r="B59" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>127372611</v>
       </c>
       <c r="B61" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>127374836</v>
       </c>
       <c r="B62" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -5427,32 +5427,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127376909</v>
+        <v>127375059</v>
       </c>
       <c r="B48" t="n">
-        <v>91352</v>
+        <v>80161</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596209</v>
+        <v>596149</v>
       </c>
       <c r="R48" t="n">
-        <v>7033789</v>
+        <v>7033864</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5524,32 +5524,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375059</v>
+        <v>127372269</v>
       </c>
       <c r="B49" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596149</v>
+        <v>596207</v>
       </c>
       <c r="R49" t="n">
-        <v>7033864</v>
+        <v>7033752</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127372269</v>
+        <v>127376909</v>
       </c>
       <c r="B50" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596207</v>
+        <v>596209</v>
       </c>
       <c r="R50" t="n">
-        <v>7033752</v>
+        <v>7033789</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5718,32 +5718,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375850</v>
+        <v>127375195</v>
       </c>
       <c r="B51" t="n">
-        <v>91352</v>
+        <v>80168</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596183</v>
+        <v>596167</v>
       </c>
       <c r="R51" t="n">
-        <v>7033841</v>
+        <v>7033854</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,7 +5815,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127372260</v>
+        <v>127375850</v>
       </c>
       <c r="B52" t="n">
         <v>91352</v>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596208</v>
+        <v>596183</v>
       </c>
       <c r="R52" t="n">
-        <v>7033752</v>
+        <v>7033841</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,32 +5912,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375195</v>
+        <v>127372260</v>
       </c>
       <c r="B53" t="n">
-        <v>80168</v>
+        <v>91352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5947,10 +5947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596167</v>
+        <v>596208</v>
       </c>
       <c r="R53" t="n">
-        <v>7033854</v>
+        <v>7033752</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96989616</v>
+        <v>119405249</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596181.3047910099</v>
+        <v>596086</v>
       </c>
       <c r="R2" t="n">
-        <v>7033788.468385997</v>
+        <v>7033887</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96989515</v>
+        <v>96989743</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596169.0229001306</v>
+        <v>596174</v>
       </c>
       <c r="R3" t="n">
-        <v>7033734.323413826</v>
+        <v>7033762</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +841,9 @@
           <t>2021-11-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,12 +873,7 @@
         <v>96989795</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,12 +890,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596195.7649048055</v>
+        <v>596196</v>
       </c>
       <c r="R4" t="n">
-        <v>7033755.293872612</v>
+        <v>7033756</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +939,9 @@
           <t>2021-11-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +968,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96989804</v>
+        <v>119404018</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +979,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596195.8457360538</v>
+        <v>596169</v>
       </c>
       <c r="R5" t="n">
-        <v>7033752.607522741</v>
+        <v>7033732</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1033,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,27 +1053,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96989743</v>
+        <v>119404449</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,29 +1085,28 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596174.9127996654</v>
+        <v>596155</v>
       </c>
       <c r="R6" t="n">
-        <v>7033762.284710402</v>
+        <v>7033757</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1130,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,49 +1150,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119403950</v>
+        <v>119404480</v>
       </c>
       <c r="B7" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1197,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596166</v>
+        <v>596161</v>
       </c>
       <c r="R7" t="n">
-        <v>7033710</v>
+        <v>7033773</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,15 +1259,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119405438</v>
+        <v>119404554</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1270,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1294,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596096</v>
+        <v>596173</v>
       </c>
       <c r="R8" t="n">
-        <v>7033869</v>
+        <v>7033767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,15 +1356,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119404211</v>
+        <v>119405257</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,21 +1367,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1391,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596165</v>
+        <v>596086</v>
       </c>
       <c r="R9" t="n">
-        <v>7033748</v>
+        <v>7033872</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,11 +1427,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,37 +1453,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119404772</v>
+        <v>119405506</v>
       </c>
       <c r="B10" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,13 +1488,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596134</v>
+        <v>596103</v>
       </c>
       <c r="R10" t="n">
-        <v>7033839</v>
+        <v>7033844</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,37 +1550,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119405182</v>
+        <v>119405876</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,13 +1585,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596091</v>
+        <v>596208</v>
       </c>
       <c r="R11" t="n">
-        <v>7033883</v>
+        <v>7033772</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,15 +1647,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119405876</v>
+        <v>119406029</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,12 +1667,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,13 +1682,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596208</v>
+        <v>596211</v>
       </c>
       <c r="R12" t="n">
-        <v>7033772</v>
+        <v>7033787</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,37 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119404184</v>
+        <v>119406389</v>
       </c>
       <c r="B13" t="n">
-        <v>91271</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596174</v>
+        <v>596218</v>
       </c>
       <c r="R13" t="n">
-        <v>7033749</v>
+        <v>7033803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,15 +1841,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119404711</v>
+        <v>123255954</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,37 +1852,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596153</v>
+        <v>596185</v>
       </c>
       <c r="R14" t="n">
-        <v>7033810</v>
+        <v>7033739</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,17 +1906,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På sälg och gran</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,27 +1926,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119404016</v>
+        <v>123256531</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,37 +1949,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596165</v>
+        <v>596223</v>
       </c>
       <c r="R15" t="n">
-        <v>7033725</v>
+        <v>7033854</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,12 +2003,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,27 +2023,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119404018</v>
+        <v>127372251</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,28 +2055,28 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596169</v>
+        <v>596208</v>
       </c>
       <c r="R16" t="n">
-        <v>7033732</v>
+        <v>7033752</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2238,12 +2100,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,27 +2120,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119404639</v>
+        <v>127375798</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,37 +2143,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596163</v>
+        <v>596193</v>
       </c>
       <c r="R17" t="n">
-        <v>7033783</v>
+        <v>7033848</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2340,12 +2197,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,27 +2217,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119405163</v>
+        <v>127376554</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,37 +2240,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596090</v>
+        <v>596215</v>
       </c>
       <c r="R18" t="n">
-        <v>7033871</v>
+        <v>7033836</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,12 +2294,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,49 +2314,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119405506</v>
+        <v>119404184</v>
       </c>
       <c r="B19" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2361,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596103</v>
+        <v>596174</v>
       </c>
       <c r="R19" t="n">
-        <v>7033844</v>
+        <v>7033749</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,15 +2423,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119404449</v>
+        <v>96989616</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,37 +2434,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596155</v>
+        <v>596181</v>
       </c>
       <c r="R20" t="n">
-        <v>7033757</v>
+        <v>7033788</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2646,12 +2489,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-11-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-11-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2666,27 +2519,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119404153</v>
+        <v>119404016</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596163</v>
+        <v>596165</v>
       </c>
       <c r="R21" t="n">
-        <v>7033740</v>
+        <v>7033725</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,15 +2628,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119404554</v>
+        <v>119405675</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,21 +2639,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,13 +2663,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596173</v>
+        <v>596110</v>
       </c>
       <c r="R22" t="n">
-        <v>7033767</v>
+        <v>7033810</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2882,15 +2725,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119406029</v>
+        <v>123255552</v>
       </c>
       <c r="B23" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,37 +2736,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596211</v>
+        <v>596192</v>
       </c>
       <c r="R23" t="n">
-        <v>7033787</v>
+        <v>7033765</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2952,12 +2790,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2972,27 +2810,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119405782</v>
+        <v>123256126</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,34 +2833,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596160</v>
+        <v>596202</v>
       </c>
       <c r="R24" t="n">
-        <v>7033799</v>
+        <v>7033790</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3054,12 +2887,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,27 +2907,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119405732</v>
+        <v>123256408</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,34 +2930,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596131</v>
+        <v>596171</v>
       </c>
       <c r="R25" t="n">
-        <v>7033799</v>
+        <v>7033849</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3156,12 +2984,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,27 +3004,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119405675</v>
+        <v>127372260</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,17 +3047,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596110</v>
+        <v>596208</v>
       </c>
       <c r="R26" t="n">
-        <v>7033810</v>
+        <v>7033752</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,12 +3081,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3278,27 +3101,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119404099</v>
+        <v>127374492</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,37 +3124,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596160</v>
+        <v>596186</v>
       </c>
       <c r="R27" t="n">
-        <v>7033738</v>
+        <v>7033816</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3360,12 +3178,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3380,27 +3198,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119405257</v>
+        <v>127374649</v>
       </c>
       <c r="B28" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3408,37 +3221,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596086</v>
+        <v>596191</v>
       </c>
       <c r="R28" t="n">
-        <v>7033872</v>
+        <v>7033805</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3462,12 +3275,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3482,27 +3295,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119404480</v>
+        <v>127375602</v>
       </c>
       <c r="B29" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,37 +3318,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596161</v>
+        <v>596167</v>
       </c>
       <c r="R29" t="n">
-        <v>7033773</v>
+        <v>7033873</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3564,12 +3372,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3584,65 +3392,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119405176</v>
+        <v>127375850</v>
       </c>
       <c r="B30" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596085</v>
+        <v>596183</v>
       </c>
       <c r="R30" t="n">
-        <v>7033865</v>
+        <v>7033841</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3666,12 +3469,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3686,66 +3489,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123255199</v>
+        <v>127376403</v>
       </c>
       <c r="B31" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596170</v>
+        <v>596203</v>
       </c>
       <c r="R31" t="n">
-        <v>7033820</v>
+        <v>7033831</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3772,12 +3566,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3804,54 +3598,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123255234</v>
+        <v>127376909</v>
       </c>
       <c r="B32" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596160</v>
+        <v>596209</v>
       </c>
       <c r="R32" t="n">
-        <v>7033817</v>
+        <v>7033789</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3878,12 +3663,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3910,15 +3695,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123255954</v>
+        <v>127377453</v>
       </c>
       <c r="B33" t="n">
-        <v>91277</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3926,21 +3706,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3950,10 +3730,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596185</v>
+        <v>596164</v>
       </c>
       <c r="R33" t="n">
-        <v>7033739</v>
+        <v>7033777</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3980,12 +3760,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4012,57 +3792,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123255893</v>
+        <v>96989515</v>
       </c>
       <c r="B34" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596178</v>
+        <v>596169</v>
       </c>
       <c r="R34" t="n">
-        <v>7033743</v>
+        <v>7033734</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4086,12 +3858,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4106,49 +3878,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123256408</v>
+        <v>127372611</v>
       </c>
       <c r="B35" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4158,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596171</v>
+        <v>596196</v>
       </c>
       <c r="R35" t="n">
-        <v>7033849</v>
+        <v>7033769</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4188,12 +3955,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4220,15 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123255986</v>
+        <v>127376674</v>
       </c>
       <c r="B36" t="n">
-        <v>79898</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4236,21 +3998,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4260,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596183</v>
+        <v>596197</v>
       </c>
       <c r="R36" t="n">
-        <v>7033741</v>
+        <v>7033813</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4290,12 +4052,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4322,37 +4084,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123254018</v>
+        <v>127376969</v>
       </c>
       <c r="B37" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4362,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596115</v>
+        <v>596224</v>
       </c>
       <c r="R37" t="n">
-        <v>7033816</v>
+        <v>7033785</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4392,12 +4149,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4424,15 +4181,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123256126</v>
+        <v>96989804</v>
       </c>
       <c r="B38" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4440,37 +4192,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596202</v>
+        <v>596196</v>
       </c>
       <c r="R38" t="n">
-        <v>7033790</v>
+        <v>7033753</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4494,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4514,27 +4267,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123255552</v>
+        <v>119404099</v>
       </c>
       <c r="B39" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4542,37 +4290,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596192</v>
+        <v>596160</v>
       </c>
       <c r="R39" t="n">
-        <v>7033765</v>
+        <v>7033738</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4596,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4616,69 +4364,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123256248</v>
+        <v>119404153</v>
       </c>
       <c r="B40" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596180</v>
+        <v>596163</v>
       </c>
       <c r="R40" t="n">
-        <v>7033809</v>
+        <v>7033740</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4702,12 +4441,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4722,27 +4461,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123253931</v>
+        <v>119404639</v>
       </c>
       <c r="B41" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4770,17 +4504,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596135</v>
+        <v>596163</v>
       </c>
       <c r="R41" t="n">
-        <v>7033851</v>
+        <v>7033783</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4804,12 +4538,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4824,22 +4558,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127376403</v>
+        <v>119404711</v>
       </c>
       <c r="B42" t="n">
-        <v>91352</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,37 +4581,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596203</v>
+        <v>596153</v>
       </c>
       <c r="R42" t="n">
-        <v>7033831</v>
+        <v>7033810</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4901,12 +4635,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På sälg och gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4921,22 +4660,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127377453</v>
+        <v>119405163</v>
       </c>
       <c r="B43" t="n">
-        <v>91352</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4944,37 +4683,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596164</v>
+        <v>596090</v>
       </c>
       <c r="R43" t="n">
-        <v>7033777</v>
+        <v>7033871</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4998,12 +4737,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5018,69 +4757,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127376010</v>
+        <v>119405438</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596194</v>
+        <v>596096</v>
       </c>
       <c r="R44" t="n">
-        <v>7033844</v>
+        <v>7033869</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5104,12 +4834,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5124,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127372251</v>
+        <v>119405732</v>
       </c>
       <c r="B45" t="n">
-        <v>91648</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5147,34 +4877,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596208</v>
+        <v>596131</v>
       </c>
       <c r="R45" t="n">
-        <v>7033752</v>
+        <v>7033799</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5201,12 +4931,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5221,22 +4951,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375798</v>
+        <v>119405782</v>
       </c>
       <c r="B46" t="n">
-        <v>91648</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5244,34 +4974,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596193</v>
+        <v>596160</v>
       </c>
       <c r="R46" t="n">
-        <v>7033848</v>
+        <v>7033799</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5298,12 +5028,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5318,22 +5048,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127374649</v>
+        <v>123253931</v>
       </c>
       <c r="B47" t="n">
-        <v>91352</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5341,34 +5071,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>596191</v>
+        <v>596135</v>
       </c>
       <c r="R47" t="n">
-        <v>7033805</v>
+        <v>7033851</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5395,12 +5125,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5427,32 +5157,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375059</v>
+        <v>123254018</v>
       </c>
       <c r="B48" t="n">
-        <v>80161</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596149</v>
+        <v>596115</v>
       </c>
       <c r="R48" t="n">
-        <v>7033864</v>
+        <v>7033816</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5492,12 +5222,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5527,7 +5257,7 @@
         <v>127372269</v>
       </c>
       <c r="B49" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5621,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127376909</v>
+        <v>127375177</v>
       </c>
       <c r="B50" t="n">
-        <v>91352</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,21 +5362,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596209</v>
+        <v>596172</v>
       </c>
       <c r="R50" t="n">
-        <v>7033789</v>
+        <v>7033852</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5718,32 +5448,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375195</v>
+        <v>127375277</v>
       </c>
       <c r="B51" t="n">
-        <v>80168</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5753,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596167</v>
+        <v>596162</v>
       </c>
       <c r="R51" t="n">
-        <v>7033854</v>
+        <v>7033857</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5815,10 +5545,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375850</v>
+        <v>127375356</v>
       </c>
       <c r="B52" t="n">
-        <v>91352</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5826,21 +5556,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5850,10 +5580,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596183</v>
+        <v>596191</v>
       </c>
       <c r="R52" t="n">
-        <v>7033841</v>
+        <v>7033864</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,32 +5642,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127372260</v>
+        <v>127375927</v>
       </c>
       <c r="B53" t="n">
-        <v>91352</v>
+        <v>80460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5947,10 +5677,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596208</v>
+        <v>596203</v>
       </c>
       <c r="R53" t="n">
-        <v>7033752</v>
+        <v>7033839</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6009,52 +5739,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127377215</v>
+        <v>119405182</v>
       </c>
       <c r="B54" t="n">
-        <v>98470</v>
+        <v>80461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596190</v>
+        <v>596091</v>
       </c>
       <c r="R54" t="n">
-        <v>7033789</v>
+        <v>7033883</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6078,12 +5804,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6098,22 +5824,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127376674</v>
+        <v>119405735</v>
       </c>
       <c r="B55" t="n">
-        <v>91317</v>
+        <v>80461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6121,37 +5847,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>596197</v>
+        <v>596115</v>
       </c>
       <c r="R55" t="n">
-        <v>7033813</v>
+        <v>7033799</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6175,12 +5901,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6195,60 +5921,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127375177</v>
+        <v>119407127</v>
       </c>
       <c r="B56" t="n">
-        <v>80132</v>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596172</v>
+        <v>596186</v>
       </c>
       <c r="R56" t="n">
-        <v>7033852</v>
+        <v>7033720</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6272,12 +5998,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6292,22 +6018,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127375927</v>
+        <v>123255986</v>
       </c>
       <c r="B57" t="n">
-        <v>80160</v>
+        <v>80461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,21 +6041,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6339,10 +6065,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596203</v>
+        <v>596183</v>
       </c>
       <c r="R57" t="n">
-        <v>7033839</v>
+        <v>7033741</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6369,12 +6095,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6401,32 +6127,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127375277</v>
+        <v>127375059</v>
       </c>
       <c r="B58" t="n">
-        <v>80132</v>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6436,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>596162</v>
+        <v>596149</v>
       </c>
       <c r="R58" t="n">
-        <v>7033857</v>
+        <v>7033864</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6498,32 +6224,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127374492</v>
+        <v>127375362</v>
       </c>
       <c r="B59" t="n">
-        <v>91352</v>
+        <v>80461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6533,10 +6259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>596186</v>
+        <v>596192</v>
       </c>
       <c r="R59" t="n">
-        <v>7033816</v>
+        <v>7033863</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6595,10 +6321,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127375316</v>
+        <v>119405176</v>
       </c>
       <c r="B60" t="n">
-        <v>80167</v>
+        <v>80467</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6626,17 +6352,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>596161</v>
+        <v>596085</v>
       </c>
       <c r="R60" t="n">
-        <v>7033859</v>
+        <v>7033865</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6660,12 +6386,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6680,22 +6406,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127372611</v>
+        <v>127375316</v>
       </c>
       <c r="B61" t="n">
-        <v>91317</v>
+        <v>80467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6703,21 +6429,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6727,10 +6453,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>596196</v>
+        <v>596161</v>
       </c>
       <c r="R61" t="n">
-        <v>7033769</v>
+        <v>7033859</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6789,10 +6515,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127374836</v>
+        <v>119403950</v>
       </c>
       <c r="B62" t="n">
-        <v>97347</v>
+        <v>80468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6800,37 +6526,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>596170</v>
+        <v>596166</v>
       </c>
       <c r="R62" t="n">
-        <v>7033847</v>
+        <v>7033710</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6854,12 +6580,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6874,15 +6600,1310 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>119404772</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>596134</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7033839</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127375195</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>596167</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7033854</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AX64" t="inlineStr">
         <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127375762</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>596188</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7033865</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>119404211</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>596165</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7033748</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>123255199</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>596170</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7033820</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>123255234</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>596160</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7033817</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>123255893</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>596178</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7033743</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>123256248</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>596180</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7033809</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127376010</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>596194</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7033844</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127377215</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>596190</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7033789</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127374836</v>
+      </c>
+      <c r="B73" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>596170</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7033847</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>119405099</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>596077</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7033856</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>119405334</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>596083</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7033890</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405249</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96989743</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96989795</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1062,6 +1082,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404018</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1184,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404449</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1256,6 +1286,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404480</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1353,6 +1388,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404554</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1450,6 +1490,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405257</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1547,6 +1592,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405506</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1644,6 +1694,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405876</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1741,6 +1796,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119406029</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1838,6 +1898,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119406389</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1935,6 +2000,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255954</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2032,6 +2102,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123256531</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2129,6 +2204,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127372251</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2226,6 +2306,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375798</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2323,6 +2408,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127376554</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2420,6 +2510,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404184</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2528,6 +2623,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96989616</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2625,6 +2725,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404016</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2722,6 +2827,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405675</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2819,6 +2929,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255552</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2916,6 +3031,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123256126</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3013,6 +3133,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123256408</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3110,6 +3235,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127372260</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3207,6 +3337,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127374492</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3304,6 +3439,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127374649</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3401,6 +3541,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375602</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3498,6 +3643,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375850</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3595,6 +3745,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127376403</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3692,6 +3847,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127376909</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3789,6 +3949,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127377453</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3887,6 +4052,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96989515</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3984,6 +4154,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127372611</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4081,6 +4256,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127376674</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4178,6 +4358,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127376969</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4276,6 +4461,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96989804</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4373,6 +4563,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404099</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4470,6 +4665,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404153</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4567,6 +4767,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404639</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4669,6 +4874,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404711</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4766,6 +4976,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405163</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4863,6 +5078,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405438</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4960,6 +5180,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405732</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5057,6 +5282,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405782</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5154,6 +5384,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123253931</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5251,6 +5486,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123254018</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5348,6 +5588,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127372269</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5445,6 +5690,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375177</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5542,6 +5792,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375277</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5639,6 +5894,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375356</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5736,6 +5996,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375927</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5833,6 +6098,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405182</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5930,6 +6200,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405735</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6027,6 +6302,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119407127</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6124,6 +6404,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255986</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6221,6 +6506,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375059</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6318,6 +6608,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375362</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6415,6 +6710,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405176</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6512,6 +6812,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375316</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6609,6 +6914,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119403950</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6706,6 +7016,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404772</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6803,6 +7118,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375195</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6900,6 +7220,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375762</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7002,6 +7327,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119404211</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7103,6 +7433,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255199</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7204,6 +7539,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255234</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7305,6 +7645,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255893</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7406,6 +7751,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123256248</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7512,6 +7862,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127376010</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7613,6 +7968,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127377215</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7710,6 +8070,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127374836</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7807,6 +8172,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405099</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7904,8 +8274,89 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405334</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ75"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3957,10 +3957,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96989515</v>
+        <v>135597226</v>
       </c>
       <c r="B34" t="n">
-        <v>92369</v>
+        <v>91974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3968,38 +3968,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>596169</v>
       </c>
       <c r="R34" t="n">
-        <v>7033734</v>
+        <v>7033731</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4023,12 +4022,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4039,69 +4038,84 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96989515</t>
+          <t>https://artportalen.se/Sighting/135597226</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127372611</v>
+        <v>135597232</v>
       </c>
       <c r="B35" t="n">
-        <v>91872</v>
+        <v>91974</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596196</v>
+        <v>596185</v>
       </c>
       <c r="R35" t="n">
-        <v>7033769</v>
+        <v>7033767</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4125,12 +4139,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4141,69 +4155,85 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127372611</t>
+          <t>https://artportalen.se/Sighting/135597232</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127376674</v>
+        <v>96989515</v>
       </c>
       <c r="B36" t="n">
-        <v>91872</v>
+        <v>92369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596197</v>
+        <v>596169</v>
       </c>
       <c r="R36" t="n">
-        <v>7033813</v>
+        <v>7033734</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4227,12 +4257,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,65 +4277,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127376674</t>
+          <t>https://artportalen.se/Sighting/96989515</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127376969</v>
+        <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>91872</v>
+        <v>92326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>2064</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596224</v>
+        <v>596189</v>
       </c>
       <c r="R37" t="n">
-        <v>7033785</v>
+        <v>7033822</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4329,86 +4359,105 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Vitgul Skeletocutis på död violticka</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127376969</t>
+          <t>https://artportalen.se/Sighting/135597236</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96989804</v>
+        <v>127372611</v>
       </c>
       <c r="B38" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
         <v>596196</v>
       </c>
       <c r="R38" t="n">
-        <v>7033753</v>
+        <v>7033769</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4432,12 +4481,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4452,65 +4501,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96989804</t>
+          <t>https://artportalen.se/Sighting/127372611</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119404099</v>
+        <v>127376674</v>
       </c>
       <c r="B39" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596160</v>
+        <v>596197</v>
       </c>
       <c r="R39" t="n">
-        <v>7033738</v>
+        <v>7033813</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4534,12 +4583,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4554,65 +4603,65 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404099</t>
+          <t>https://artportalen.se/Sighting/127376674</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119404153</v>
+        <v>127376969</v>
       </c>
       <c r="B40" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596163</v>
+        <v>596224</v>
       </c>
       <c r="R40" t="n">
-        <v>7033740</v>
+        <v>7033785</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4636,12 +4685,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,62 +4705,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404153</t>
+          <t>https://artportalen.se/Sighting/127376969</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119404639</v>
+        <v>135597229</v>
       </c>
       <c r="B41" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596163</v>
+        <v>596178</v>
       </c>
       <c r="R41" t="n">
-        <v>7033783</v>
+        <v>7033741</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4738,12 +4787,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,24 +4807,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404639</t>
+          <t>https://artportalen.se/Sighting/135597229</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119404711</v>
+        <v>96989804</v>
       </c>
       <c r="B42" t="n">
         <v>80432</v>
@@ -4804,19 +4853,20 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596153</v>
+        <v>596196</v>
       </c>
       <c r="R42" t="n">
-        <v>7033810</v>
+        <v>7033753</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4840,17 +4890,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På sälg och gran</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4865,24 +4910,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404711</t>
+          <t>https://artportalen.se/Sighting/96989804</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119405163</v>
+        <v>119404099</v>
       </c>
       <c r="B43" t="n">
         <v>80432</v>
@@ -4917,13 +4962,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596090</v>
+        <v>596160</v>
       </c>
       <c r="R43" t="n">
-        <v>7033871</v>
+        <v>7033738</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4978,13 +5023,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405163</t>
+          <t>https://artportalen.se/Sighting/119404099</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119405438</v>
+        <v>119404153</v>
       </c>
       <c r="B44" t="n">
         <v>80432</v>
@@ -5019,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596096</v>
+        <v>596163</v>
       </c>
       <c r="R44" t="n">
-        <v>7033869</v>
+        <v>7033740</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5080,13 +5125,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405438</t>
+          <t>https://artportalen.se/Sighting/119404153</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119405732</v>
+        <v>119404639</v>
       </c>
       <c r="B45" t="n">
         <v>80432</v>
@@ -5121,13 +5166,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596131</v>
+        <v>596163</v>
       </c>
       <c r="R45" t="n">
-        <v>7033799</v>
+        <v>7033783</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5182,13 +5227,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405732</t>
+          <t>https://artportalen.se/Sighting/119404639</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119405782</v>
+        <v>119404711</v>
       </c>
       <c r="B46" t="n">
         <v>80432</v>
@@ -5223,13 +5268,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596160</v>
+        <v>596153</v>
       </c>
       <c r="R46" t="n">
-        <v>7033799</v>
+        <v>7033810</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5259,6 +5304,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På sälg och gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,13 +5334,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405782</t>
+          <t>https://artportalen.se/Sighting/119404711</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123253931</v>
+        <v>119405163</v>
       </c>
       <c r="B47" t="n">
         <v>80432</v>
@@ -5321,17 +5371,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>596135</v>
+        <v>596090</v>
       </c>
       <c r="R47" t="n">
-        <v>7033851</v>
+        <v>7033871</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5355,12 +5405,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5375,24 +5425,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123253931</t>
+          <t>https://artportalen.se/Sighting/119405163</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123254018</v>
+        <v>119405438</v>
       </c>
       <c r="B48" t="n">
         <v>80432</v>
@@ -5423,17 +5473,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596115</v>
+        <v>596096</v>
       </c>
       <c r="R48" t="n">
-        <v>7033816</v>
+        <v>7033869</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5457,12 +5507,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5477,24 +5527,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123254018</t>
+          <t>https://artportalen.se/Sighting/119405438</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127372269</v>
+        <v>119405732</v>
       </c>
       <c r="B49" t="n">
         <v>80432</v>
@@ -5525,14 +5575,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596207</v>
+        <v>596131</v>
       </c>
       <c r="R49" t="n">
-        <v>7033752</v>
+        <v>7033799</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5559,12 +5609,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5579,24 +5629,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127372269</t>
+          <t>https://artportalen.se/Sighting/119405732</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127375177</v>
+        <v>119405782</v>
       </c>
       <c r="B50" t="n">
         <v>80432</v>
@@ -5627,14 +5677,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596172</v>
+        <v>596160</v>
       </c>
       <c r="R50" t="n">
-        <v>7033852</v>
+        <v>7033799</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5661,12 +5711,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5681,24 +5731,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375177</t>
+          <t>https://artportalen.se/Sighting/119405782</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375277</v>
+        <v>123253931</v>
       </c>
       <c r="B51" t="n">
         <v>80432</v>
@@ -5733,10 +5783,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596162</v>
+        <v>596135</v>
       </c>
       <c r="R51" t="n">
-        <v>7033857</v>
+        <v>7033851</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5763,12 +5813,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5794,13 +5844,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375277</t>
+          <t>https://artportalen.se/Sighting/123253931</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375356</v>
+        <v>123254018</v>
       </c>
       <c r="B52" t="n">
         <v>80432</v>
@@ -5835,10 +5885,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596191</v>
+        <v>596115</v>
       </c>
       <c r="R52" t="n">
-        <v>7033864</v>
+        <v>7033816</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5865,12 +5915,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5896,38 +5946,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375356</t>
+          <t>https://artportalen.se/Sighting/123254018</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375927</v>
+        <v>127372269</v>
       </c>
       <c r="B53" t="n">
-        <v>80460</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5987,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596203</v>
+        <v>596207</v>
       </c>
       <c r="R53" t="n">
-        <v>7033839</v>
+        <v>7033752</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5998,54 +6048,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375927</t>
+          <t>https://artportalen.se/Sighting/127372269</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119405182</v>
+        <v>127375177</v>
       </c>
       <c r="B54" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596091</v>
+        <v>596172</v>
       </c>
       <c r="R54" t="n">
-        <v>7033883</v>
+        <v>7033852</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6069,12 +6119,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6089,65 +6139,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405182</t>
+          <t>https://artportalen.se/Sighting/127375177</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119405735</v>
+        <v>127375277</v>
       </c>
       <c r="B55" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>596115</v>
+        <v>596162</v>
       </c>
       <c r="R55" t="n">
-        <v>7033799</v>
+        <v>7033857</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6171,12 +6221,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6191,65 +6241,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405735</t>
+          <t>https://artportalen.se/Sighting/127375277</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119407127</v>
+        <v>127375356</v>
       </c>
       <c r="B56" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596186</v>
+        <v>596191</v>
       </c>
       <c r="R56" t="n">
-        <v>7033720</v>
+        <v>7033864</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6273,12 +6323,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6293,65 +6343,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119407127</t>
+          <t>https://artportalen.se/Sighting/127375356</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123255986</v>
+        <v>135597231</v>
       </c>
       <c r="B57" t="n">
-        <v>80461</v>
+        <v>80488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596183</v>
+        <v>596178</v>
       </c>
       <c r="R57" t="n">
-        <v>7033741</v>
+        <v>7033753</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6375,12 +6425,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6395,27 +6445,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123255986</t>
+          <t>https://artportalen.se/Sighting/135597231</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127375059</v>
+        <v>127375927</v>
       </c>
       <c r="B58" t="n">
-        <v>80461</v>
+        <v>80460</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6423,21 +6473,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6447,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>596149</v>
+        <v>596203</v>
       </c>
       <c r="R58" t="n">
-        <v>7033864</v>
+        <v>7033839</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6508,13 +6558,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375059</t>
+          <t>https://artportalen.se/Sighting/127375927</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127375362</v>
+        <v>119405182</v>
       </c>
       <c r="B59" t="n">
         <v>80461</v>
@@ -6545,17 +6595,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>596192</v>
+        <v>596091</v>
       </c>
       <c r="R59" t="n">
-        <v>7033863</v>
+        <v>7033883</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6579,12 +6629,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,27 +6649,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375362</t>
+          <t>https://artportalen.se/Sighting/119405182</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119405176</v>
+        <v>119405735</v>
       </c>
       <c r="B60" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6627,21 +6677,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6651,13 +6701,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>596085</v>
+        <v>596115</v>
       </c>
       <c r="R60" t="n">
-        <v>7033865</v>
+        <v>7033799</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6712,16 +6762,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405176</t>
+          <t>https://artportalen.se/Sighting/119405735</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127375316</v>
+        <v>119407127</v>
       </c>
       <c r="B61" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6729,37 +6779,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>596161</v>
+        <v>596186</v>
       </c>
       <c r="R61" t="n">
-        <v>7033859</v>
+        <v>7033720</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6783,12 +6833,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6803,27 +6853,27 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375316</t>
+          <t>https://artportalen.se/Sighting/119407127</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119403950</v>
+        <v>123255986</v>
       </c>
       <c r="B62" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6831,37 +6881,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>596166</v>
+        <v>596183</v>
       </c>
       <c r="R62" t="n">
-        <v>7033710</v>
+        <v>7033741</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6885,12 +6935,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6905,27 +6955,27 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119403950</t>
+          <t>https://artportalen.se/Sighting/123255986</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119404772</v>
+        <v>127375059</v>
       </c>
       <c r="B63" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6933,34 +6983,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>596134</v>
+        <v>596149</v>
       </c>
       <c r="R63" t="n">
-        <v>7033839</v>
+        <v>7033864</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6987,12 +7037,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,27 +7057,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404772</t>
+          <t>https://artportalen.se/Sighting/127375059</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127375195</v>
+        <v>127375362</v>
       </c>
       <c r="B64" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7035,21 +7085,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7059,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>596167</v>
+        <v>596192</v>
       </c>
       <c r="R64" t="n">
-        <v>7033854</v>
+        <v>7033863</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7120,16 +7170,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375195</t>
+          <t>https://artportalen.se/Sighting/127375362</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127375762</v>
+        <v>135597230</v>
       </c>
       <c r="B65" t="n">
-        <v>80468</v>
+        <v>80493</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7137,37 +7187,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>596188</v>
+        <v>596177</v>
       </c>
       <c r="R65" t="n">
-        <v>7033865</v>
+        <v>7033751</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7191,12 +7241,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7211,27 +7261,27 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375762</t>
+          <t>https://artportalen.se/Sighting/135597230</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119404211</v>
+        <v>119405176</v>
       </c>
       <c r="B66" t="n">
-        <v>57950</v>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7239,21 +7289,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7263,13 +7313,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>596165</v>
+        <v>596085</v>
       </c>
       <c r="R66" t="n">
-        <v>7033748</v>
+        <v>7033865</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7299,11 +7349,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7329,55 +7374,51 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404211</t>
+          <t>https://artportalen.se/Sighting/119405176</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123255199</v>
+        <v>127375316</v>
       </c>
       <c r="B67" t="n">
-        <v>99118</v>
+        <v>80467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>596170</v>
+        <v>596161</v>
       </c>
       <c r="R67" t="n">
-        <v>7033820</v>
+        <v>7033859</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7404,12 +7445,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7435,58 +7476,54 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123255199</t>
+          <t>https://artportalen.se/Sighting/127375316</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123255234</v>
+        <v>135597225</v>
       </c>
       <c r="B68" t="n">
-        <v>99118</v>
+        <v>80499</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>596160</v>
+        <v>596167</v>
       </c>
       <c r="R68" t="n">
-        <v>7033817</v>
+        <v>7033717</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7510,12 +7547,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7530,69 +7567,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123255234</t>
+          <t>https://artportalen.se/Sighting/135597225</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123255893</v>
+        <v>119403950</v>
       </c>
       <c r="B69" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>596178</v>
+        <v>596166</v>
       </c>
       <c r="R69" t="n">
-        <v>7033743</v>
+        <v>7033710</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7616,12 +7649,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7636,66 +7669,62 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123255893</t>
+          <t>https://artportalen.se/Sighting/119403950</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123256248</v>
+        <v>119404772</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>596180</v>
+        <v>596134</v>
       </c>
       <c r="R70" t="n">
-        <v>7033809</v>
+        <v>7033839</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7722,12 +7751,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7742,71 +7771,62 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123256248</t>
+          <t>https://artportalen.se/Sighting/119404772</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127376010</v>
+        <v>127375195</v>
       </c>
       <c r="B71" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>596194</v>
+        <v>596167</v>
       </c>
       <c r="R71" t="n">
-        <v>7033844</v>
+        <v>7033854</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7864,55 +7884,51 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127376010</t>
+          <t>https://artportalen.se/Sighting/127375195</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127377215</v>
+        <v>127375762</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>596190</v>
+        <v>596188</v>
       </c>
       <c r="R72" t="n">
-        <v>7033789</v>
+        <v>7033865</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7970,16 +7986,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127377215</t>
+          <t>https://artportalen.se/Sighting/127375762</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127374836</v>
+        <v>119404211</v>
       </c>
       <c r="B73" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7987,37 +8003,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>596170</v>
+        <v>596165</v>
       </c>
       <c r="R73" t="n">
-        <v>7033847</v>
+        <v>7033748</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8041,12 +8057,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8061,65 +8082,69 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127374836</t>
+          <t>https://artportalen.se/Sighting/119404211</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119405099</v>
+        <v>123255199</v>
       </c>
       <c r="B74" t="n">
-        <v>101228</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>596077</v>
+        <v>596170</v>
       </c>
       <c r="R74" t="n">
-        <v>7033856</v>
+        <v>7033820</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8143,12 +8168,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8163,65 +8188,69 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405099</t>
+          <t>https://artportalen.se/Sighting/123255199</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119405334</v>
+        <v>123255234</v>
       </c>
       <c r="B75" t="n">
-        <v>101228</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>596083</v>
+        <v>596160</v>
       </c>
       <c r="R75" t="n">
-        <v>7033890</v>
+        <v>7033817</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8245,12 +8274,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8265,18 +8294,1278 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/123255234</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>123255893</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>596178</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7033743</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255893</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123256248</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>596180</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7033809</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123256248</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127376010</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>596194</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7033844</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127376010</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127377215</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>596190</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7033789</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127377215</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135597224</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>596156</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7033710</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597224</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135597227</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>596182</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7033741</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597227</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135597234</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>596170</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7033805</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597234</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135597235</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>596171</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7033825</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597235</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127374836</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>596170</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7033847</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127374836</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>119405099</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>596077</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7033856</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405099</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>119405334</v>
+      </c>
+      <c r="B86" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>596083</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7033890</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/119405334</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135597228</v>
+      </c>
+      <c r="B87" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>253810</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skorpgrynna</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dichostereum boreale</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Pouzar) Ginns &amp; M.N.L.Lefebvre</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>596178</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7033740</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597228</t>
         </is>
       </c>
     </row>
@@ -8356,6 +9645,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3960,7 +3960,7 @@
         <v>135597226</v>
       </c>
       <c r="B34" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>135597232</v>
       </c>
       <c r="B35" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92326</v>
+        <v>92368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>135597229</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>135597231</v>
       </c>
       <c r="B57" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>135597230</v>
       </c>
       <c r="B65" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>135597225</v>
       </c>
       <c r="B68" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135597224</v>
       </c>
       <c r="B80" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>135597227</v>
       </c>
       <c r="B81" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135597234</v>
       </c>
       <c r="B82" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>135597235</v>
       </c>
       <c r="B83" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>135597228</v>
       </c>
       <c r="B87" t="n">
-        <v>92822</v>
+        <v>92864</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3960,7 +3960,7 @@
         <v>135597226</v>
       </c>
       <c r="B34" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>135597232</v>
       </c>
       <c r="B35" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92368</v>
+        <v>92395</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>135597229</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>135597231</v>
       </c>
       <c r="B57" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>135597230</v>
       </c>
       <c r="B65" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>135597225</v>
       </c>
       <c r="B68" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135597224</v>
       </c>
       <c r="B80" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>135597227</v>
       </c>
       <c r="B81" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135597234</v>
       </c>
       <c r="B82" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>135597235</v>
       </c>
       <c r="B83" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>135597228</v>
       </c>
       <c r="B87" t="n">
-        <v>92864</v>
+        <v>92891</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ75"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3957,10 +3957,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96989515</v>
+        <v>135597226</v>
       </c>
       <c r="B34" t="n">
-        <v>92369</v>
+        <v>92048</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3968,38 +3968,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>596169</v>
       </c>
       <c r="R34" t="n">
-        <v>7033734</v>
+        <v>7033731</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4023,12 +4022,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4039,69 +4038,84 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96989515</t>
+          <t>https://artportalen.se/Sighting/135597226</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127372611</v>
+        <v>135597232</v>
       </c>
       <c r="B35" t="n">
-        <v>91872</v>
+        <v>92048</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596196</v>
+        <v>596185</v>
       </c>
       <c r="R35" t="n">
-        <v>7033769</v>
+        <v>7033767</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4125,12 +4139,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4141,69 +4155,85 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127372611</t>
+          <t>https://artportalen.se/Sighting/135597232</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127376674</v>
+        <v>96989515</v>
       </c>
       <c r="B36" t="n">
-        <v>91872</v>
+        <v>92369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596197</v>
+        <v>596169</v>
       </c>
       <c r="R36" t="n">
-        <v>7033813</v>
+        <v>7033734</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4227,12 +4257,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,65 +4277,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127376674</t>
+          <t>https://artportalen.se/Sighting/96989515</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127376969</v>
+        <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>91872</v>
+        <v>92400</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>2064</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596224</v>
+        <v>596189</v>
       </c>
       <c r="R37" t="n">
-        <v>7033785</v>
+        <v>7033822</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4329,86 +4359,105 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Vitgul Skeletocutis på död violticka</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127376969</t>
+          <t>https://artportalen.se/Sighting/135597236</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96989804</v>
+        <v>127372611</v>
       </c>
       <c r="B38" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
         <v>596196</v>
       </c>
       <c r="R38" t="n">
-        <v>7033753</v>
+        <v>7033769</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4432,12 +4481,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4452,65 +4501,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96989804</t>
+          <t>https://artportalen.se/Sighting/127372611</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119404099</v>
+        <v>127376674</v>
       </c>
       <c r="B39" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596160</v>
+        <v>596197</v>
       </c>
       <c r="R39" t="n">
-        <v>7033738</v>
+        <v>7033813</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4534,12 +4583,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4554,65 +4603,65 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404099</t>
+          <t>https://artportalen.se/Sighting/127376674</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119404153</v>
+        <v>127376969</v>
       </c>
       <c r="B40" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596163</v>
+        <v>596224</v>
       </c>
       <c r="R40" t="n">
-        <v>7033740</v>
+        <v>7033785</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4636,12 +4685,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,62 +4705,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404153</t>
+          <t>https://artportalen.se/Sighting/127376969</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119404639</v>
+        <v>135597229</v>
       </c>
       <c r="B41" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596163</v>
+        <v>596178</v>
       </c>
       <c r="R41" t="n">
-        <v>7033783</v>
+        <v>7033741</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4738,12 +4787,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,24 +4807,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404639</t>
+          <t>https://artportalen.se/Sighting/135597229</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119404711</v>
+        <v>96989804</v>
       </c>
       <c r="B42" t="n">
         <v>80432</v>
@@ -4804,19 +4853,20 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596153</v>
+        <v>596196</v>
       </c>
       <c r="R42" t="n">
-        <v>7033810</v>
+        <v>7033753</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4840,17 +4890,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På sälg och gran</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4865,24 +4910,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404711</t>
+          <t>https://artportalen.se/Sighting/96989804</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119405163</v>
+        <v>119404099</v>
       </c>
       <c r="B43" t="n">
         <v>80432</v>
@@ -4917,13 +4962,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596090</v>
+        <v>596160</v>
       </c>
       <c r="R43" t="n">
-        <v>7033871</v>
+        <v>7033738</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4978,13 +5023,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405163</t>
+          <t>https://artportalen.se/Sighting/119404099</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119405438</v>
+        <v>119404153</v>
       </c>
       <c r="B44" t="n">
         <v>80432</v>
@@ -5019,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596096</v>
+        <v>596163</v>
       </c>
       <c r="R44" t="n">
-        <v>7033869</v>
+        <v>7033740</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5080,13 +5125,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405438</t>
+          <t>https://artportalen.se/Sighting/119404153</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119405732</v>
+        <v>119404639</v>
       </c>
       <c r="B45" t="n">
         <v>80432</v>
@@ -5121,13 +5166,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596131</v>
+        <v>596163</v>
       </c>
       <c r="R45" t="n">
-        <v>7033799</v>
+        <v>7033783</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5182,13 +5227,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405732</t>
+          <t>https://artportalen.se/Sighting/119404639</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119405782</v>
+        <v>119404711</v>
       </c>
       <c r="B46" t="n">
         <v>80432</v>
@@ -5223,13 +5268,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596160</v>
+        <v>596153</v>
       </c>
       <c r="R46" t="n">
-        <v>7033799</v>
+        <v>7033810</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5259,6 +5304,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På sälg och gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,13 +5334,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405782</t>
+          <t>https://artportalen.se/Sighting/119404711</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123253931</v>
+        <v>119405163</v>
       </c>
       <c r="B47" t="n">
         <v>80432</v>
@@ -5321,17 +5371,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>596135</v>
+        <v>596090</v>
       </c>
       <c r="R47" t="n">
-        <v>7033851</v>
+        <v>7033871</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5355,12 +5405,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5375,24 +5425,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123253931</t>
+          <t>https://artportalen.se/Sighting/119405163</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123254018</v>
+        <v>119405438</v>
       </c>
       <c r="B48" t="n">
         <v>80432</v>
@@ -5423,17 +5473,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596115</v>
+        <v>596096</v>
       </c>
       <c r="R48" t="n">
-        <v>7033816</v>
+        <v>7033869</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5457,12 +5507,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5477,24 +5527,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123254018</t>
+          <t>https://artportalen.se/Sighting/119405438</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127372269</v>
+        <v>119405732</v>
       </c>
       <c r="B49" t="n">
         <v>80432</v>
@@ -5525,14 +5575,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596207</v>
+        <v>596131</v>
       </c>
       <c r="R49" t="n">
-        <v>7033752</v>
+        <v>7033799</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5559,12 +5609,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5579,24 +5629,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127372269</t>
+          <t>https://artportalen.se/Sighting/119405732</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127375177</v>
+        <v>119405782</v>
       </c>
       <c r="B50" t="n">
         <v>80432</v>
@@ -5627,14 +5677,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596172</v>
+        <v>596160</v>
       </c>
       <c r="R50" t="n">
-        <v>7033852</v>
+        <v>7033799</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5661,12 +5711,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5681,24 +5731,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375177</t>
+          <t>https://artportalen.se/Sighting/119405782</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127375277</v>
+        <v>123253931</v>
       </c>
       <c r="B51" t="n">
         <v>80432</v>
@@ -5733,10 +5783,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596162</v>
+        <v>596135</v>
       </c>
       <c r="R51" t="n">
-        <v>7033857</v>
+        <v>7033851</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5763,12 +5813,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5794,13 +5844,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375277</t>
+          <t>https://artportalen.se/Sighting/123253931</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127375356</v>
+        <v>123254018</v>
       </c>
       <c r="B52" t="n">
         <v>80432</v>
@@ -5835,10 +5885,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596191</v>
+        <v>596115</v>
       </c>
       <c r="R52" t="n">
-        <v>7033864</v>
+        <v>7033816</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5865,12 +5915,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5896,38 +5946,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375356</t>
+          <t>https://artportalen.se/Sighting/123254018</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127375927</v>
+        <v>127372269</v>
       </c>
       <c r="B53" t="n">
-        <v>80460</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5987,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596203</v>
+        <v>596207</v>
       </c>
       <c r="R53" t="n">
-        <v>7033839</v>
+        <v>7033752</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5998,54 +6048,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375927</t>
+          <t>https://artportalen.se/Sighting/127372269</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119405182</v>
+        <v>127375177</v>
       </c>
       <c r="B54" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596091</v>
+        <v>596172</v>
       </c>
       <c r="R54" t="n">
-        <v>7033883</v>
+        <v>7033852</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6069,12 +6119,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6089,65 +6139,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405182</t>
+          <t>https://artportalen.se/Sighting/127375177</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119405735</v>
+        <v>127375277</v>
       </c>
       <c r="B55" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>596115</v>
+        <v>596162</v>
       </c>
       <c r="R55" t="n">
-        <v>7033799</v>
+        <v>7033857</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6171,12 +6221,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6191,65 +6241,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405735</t>
+          <t>https://artportalen.se/Sighting/127375277</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119407127</v>
+        <v>127375356</v>
       </c>
       <c r="B56" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596186</v>
+        <v>596191</v>
       </c>
       <c r="R56" t="n">
-        <v>7033720</v>
+        <v>7033864</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6273,12 +6323,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6293,65 +6343,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119407127</t>
+          <t>https://artportalen.se/Sighting/127375356</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123255986</v>
+        <v>135597231</v>
       </c>
       <c r="B57" t="n">
-        <v>80461</v>
+        <v>80556</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596183</v>
+        <v>596178</v>
       </c>
       <c r="R57" t="n">
-        <v>7033741</v>
+        <v>7033753</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6375,12 +6425,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6395,27 +6445,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123255986</t>
+          <t>https://artportalen.se/Sighting/135597231</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127375059</v>
+        <v>127375927</v>
       </c>
       <c r="B58" t="n">
-        <v>80461</v>
+        <v>80460</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6423,21 +6473,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6447,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>596149</v>
+        <v>596203</v>
       </c>
       <c r="R58" t="n">
-        <v>7033864</v>
+        <v>7033839</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6508,13 +6558,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375059</t>
+          <t>https://artportalen.se/Sighting/127375927</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127375362</v>
+        <v>119405182</v>
       </c>
       <c r="B59" t="n">
         <v>80461</v>
@@ -6545,17 +6595,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>596192</v>
+        <v>596091</v>
       </c>
       <c r="R59" t="n">
-        <v>7033863</v>
+        <v>7033883</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6579,12 +6629,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,27 +6649,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375362</t>
+          <t>https://artportalen.se/Sighting/119405182</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119405176</v>
+        <v>119405735</v>
       </c>
       <c r="B60" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6627,21 +6677,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6651,13 +6701,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>596085</v>
+        <v>596115</v>
       </c>
       <c r="R60" t="n">
-        <v>7033865</v>
+        <v>7033799</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6712,16 +6762,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405176</t>
+          <t>https://artportalen.se/Sighting/119405735</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127375316</v>
+        <v>119407127</v>
       </c>
       <c r="B61" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6729,37 +6779,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>596161</v>
+        <v>596186</v>
       </c>
       <c r="R61" t="n">
-        <v>7033859</v>
+        <v>7033720</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6783,12 +6833,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6803,27 +6853,27 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375316</t>
+          <t>https://artportalen.se/Sighting/119407127</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119403950</v>
+        <v>123255986</v>
       </c>
       <c r="B62" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6831,37 +6881,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>596166</v>
+        <v>596183</v>
       </c>
       <c r="R62" t="n">
-        <v>7033710</v>
+        <v>7033741</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6885,12 +6935,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6905,27 +6955,27 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119403950</t>
+          <t>https://artportalen.se/Sighting/123255986</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119404772</v>
+        <v>127375059</v>
       </c>
       <c r="B63" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6933,34 +6983,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>596134</v>
+        <v>596149</v>
       </c>
       <c r="R63" t="n">
-        <v>7033839</v>
+        <v>7033864</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6987,12 +7037,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,27 +7057,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404772</t>
+          <t>https://artportalen.se/Sighting/127375059</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127375195</v>
+        <v>127375362</v>
       </c>
       <c r="B64" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7035,21 +7085,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7059,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>596167</v>
+        <v>596192</v>
       </c>
       <c r="R64" t="n">
-        <v>7033854</v>
+        <v>7033863</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7120,16 +7170,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375195</t>
+          <t>https://artportalen.se/Sighting/127375362</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127375762</v>
+        <v>135597230</v>
       </c>
       <c r="B65" t="n">
-        <v>80468</v>
+        <v>80561</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7137,37 +7187,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>596188</v>
+        <v>596177</v>
       </c>
       <c r="R65" t="n">
-        <v>7033865</v>
+        <v>7033751</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7191,12 +7241,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7211,27 +7261,27 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127375762</t>
+          <t>https://artportalen.se/Sighting/135597230</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119404211</v>
+        <v>119405176</v>
       </c>
       <c r="B66" t="n">
-        <v>57950</v>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7239,21 +7289,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7263,13 +7313,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>596165</v>
+        <v>596085</v>
       </c>
       <c r="R66" t="n">
-        <v>7033748</v>
+        <v>7033865</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7299,11 +7349,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7329,55 +7374,51 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119404211</t>
+          <t>https://artportalen.se/Sighting/119405176</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123255199</v>
+        <v>127375316</v>
       </c>
       <c r="B67" t="n">
-        <v>99118</v>
+        <v>80467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>596170</v>
+        <v>596161</v>
       </c>
       <c r="R67" t="n">
-        <v>7033820</v>
+        <v>7033859</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7404,12 +7445,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7435,58 +7476,54 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123255199</t>
+          <t>https://artportalen.se/Sighting/127375316</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123255234</v>
+        <v>135597225</v>
       </c>
       <c r="B68" t="n">
-        <v>99118</v>
+        <v>80567</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Hundforsklippen, Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>596160</v>
+        <v>596167</v>
       </c>
       <c r="R68" t="n">
-        <v>7033817</v>
+        <v>7033717</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7510,12 +7547,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7530,69 +7567,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123255234</t>
+          <t>https://artportalen.se/Sighting/135597225</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123255893</v>
+        <v>119403950</v>
       </c>
       <c r="B69" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>596178</v>
+        <v>596166</v>
       </c>
       <c r="R69" t="n">
-        <v>7033743</v>
+        <v>7033710</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7616,12 +7649,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7636,66 +7669,62 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123255893</t>
+          <t>https://artportalen.se/Sighting/119403950</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123256248</v>
+        <v>119404772</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>596180</v>
+        <v>596134</v>
       </c>
       <c r="R70" t="n">
-        <v>7033809</v>
+        <v>7033839</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7722,12 +7751,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7742,71 +7771,62 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123256248</t>
+          <t>https://artportalen.se/Sighting/119404772</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127376010</v>
+        <v>127375195</v>
       </c>
       <c r="B71" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>596194</v>
+        <v>596167</v>
       </c>
       <c r="R71" t="n">
-        <v>7033844</v>
+        <v>7033854</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7864,55 +7884,51 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127376010</t>
+          <t>https://artportalen.se/Sighting/127375195</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127377215</v>
+        <v>127375762</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>80468</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>596190</v>
+        <v>596188</v>
       </c>
       <c r="R72" t="n">
-        <v>7033789</v>
+        <v>7033865</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7970,16 +7986,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127377215</t>
+          <t>https://artportalen.se/Sighting/127375762</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127374836</v>
+        <v>119404211</v>
       </c>
       <c r="B73" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7987,37 +8003,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>596170</v>
+        <v>596165</v>
       </c>
       <c r="R73" t="n">
-        <v>7033847</v>
+        <v>7033748</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8041,12 +8057,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8061,65 +8082,69 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127374836</t>
+          <t>https://artportalen.se/Sighting/119404211</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119405099</v>
+        <v>123255199</v>
       </c>
       <c r="B74" t="n">
-        <v>101228</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>596077</v>
+        <v>596170</v>
       </c>
       <c r="R74" t="n">
-        <v>7033856</v>
+        <v>7033820</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8143,12 +8168,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8163,65 +8188,69 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119405099</t>
+          <t>https://artportalen.se/Sighting/123255199</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119405334</v>
+        <v>123255234</v>
       </c>
       <c r="B75" t="n">
-        <v>101228</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>596083</v>
+        <v>596160</v>
       </c>
       <c r="R75" t="n">
-        <v>7033890</v>
+        <v>7033817</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8245,12 +8274,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8265,18 +8294,1278 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/123255234</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>123255893</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>596178</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7033743</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255893</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123256248</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>596180</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7033809</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123256248</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127376010</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>596194</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7033844</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127376010</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127377215</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>596190</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7033789</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127377215</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135597224</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>596156</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7033710</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597224</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135597227</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>596182</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7033741</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597227</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135597234</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>596170</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7033805</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597234</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135597235</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>596171</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7033825</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597235</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127374836</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Hundforsklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>596170</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7033847</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127374836</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>119405099</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>596077</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7033856</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405099</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>119405334</v>
+      </c>
+      <c r="B86" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>596083</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7033890</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/119405334</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135597228</v>
+      </c>
+      <c r="B87" t="n">
+        <v>92896</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>253810</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skorpgrynna</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dichostereum boreale</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Pouzar) Ginns &amp; M.N.L.Lefebvre</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Hundforsklippen, Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>596178</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7033740</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597228</t>
         </is>
       </c>
     </row>
@@ -8356,6 +9645,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3960,7 +3960,7 @@
         <v>135597226</v>
       </c>
       <c r="B34" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>135597232</v>
       </c>
       <c r="B35" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92400</v>
+        <v>92402</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135597224</v>
       </c>
       <c r="B80" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>135597227</v>
       </c>
       <c r="B81" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135597234</v>
       </c>
       <c r="B82" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>135597235</v>
       </c>
       <c r="B83" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>135597228</v>
       </c>
       <c r="B87" t="n">
-        <v>92896</v>
+        <v>92898</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3995,7 +3995,7 @@
         <v>596169</v>
       </c>
       <c r="R34" t="n">
-        <v>7033731</v>
+        <v>7033732</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3995,7 +3995,7 @@
         <v>596169</v>
       </c>
       <c r="R34" t="n">
-        <v>7033732</v>
+        <v>7033731</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3960,7 +3960,7 @@
         <v>135597226</v>
       </c>
       <c r="B34" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>596169</v>
       </c>
       <c r="R34" t="n">
-        <v>7033731</v>
+        <v>7033732</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4077,7 +4077,7 @@
         <v>135597232</v>
       </c>
       <c r="B35" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92402</v>
+        <v>92414</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>135597229</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>135597231</v>
       </c>
       <c r="B57" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>135597230</v>
       </c>
       <c r="B65" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>135597225</v>
       </c>
       <c r="B68" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135597224</v>
       </c>
       <c r="B80" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>135597227</v>
       </c>
       <c r="B81" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135597234</v>
       </c>
       <c r="B82" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>135597235</v>
       </c>
       <c r="B83" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>135597228</v>
       </c>
       <c r="B87" t="n">
-        <v>92898</v>
+        <v>92913</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3960,7 +3960,7 @@
         <v>135597226</v>
       </c>
       <c r="B34" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>596169</v>
       </c>
       <c r="R34" t="n">
-        <v>7033731</v>
+        <v>7033732</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4077,7 +4077,7 @@
         <v>135597232</v>
       </c>
       <c r="B35" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92414</v>
+        <v>92415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>135597229</v>
       </c>
       <c r="B41" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>135597231</v>
       </c>
       <c r="B57" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>135597230</v>
       </c>
       <c r="B65" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>135597225</v>
       </c>
       <c r="B68" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135597224</v>
       </c>
       <c r="B80" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>135597227</v>
       </c>
       <c r="B81" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135597234</v>
       </c>
       <c r="B82" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>135597235</v>
       </c>
       <c r="B83" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>135597228</v>
       </c>
       <c r="B87" t="n">
-        <v>92913</v>
+        <v>92914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -3960,7 +3960,7 @@
         <v>135597226</v>
       </c>
       <c r="B34" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>135597232</v>
       </c>
       <c r="B35" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92415</v>
+        <v>92416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135597224</v>
       </c>
       <c r="B80" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>135597227</v>
       </c>
       <c r="B81" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135597234</v>
       </c>
       <c r="B82" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>135597235</v>
       </c>
       <c r="B83" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>135597228</v>
       </c>
       <c r="B87" t="n">
-        <v>92914</v>
+        <v>92915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4323,6 +4323,9 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hundforsklippen, Näsåker, Ång</t>
@@ -4376,8 +4379,9 @@
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92416</v>
+        <v>92417</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92417</v>
+        <v>92423</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92423</v>
+        <v>92424</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92424</v>
+        <v>92430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92430</v>
+        <v>92437</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92437</v>
+        <v>92438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92438</v>
+        <v>92451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28161-2024 artfynd.xlsx
+++ b/artfynd/A 28161-2024 artfynd.xlsx
@@ -4297,7 +4297,7 @@
         <v>135597236</v>
       </c>
       <c r="B37" t="n">
-        <v>92451</v>
+        <v>92452</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
